--- a/backend/app/templates/hours_export.xlsx
+++ b/backend/app/templates/hours_export.xlsx
@@ -179,7 +179,7 @@
     <numFmt numFmtId="179" formatCode="[$-404]aaa;@"/>
     <numFmt numFmtId="180" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="55">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -251,12 +251,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1369,48 +1363,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="37">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="0">
+    <xf numFmtId="42" fontId="34" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="34" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="35" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="38">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1420,104 +1417,101 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="39">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="40">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="23" borderId="41">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="23" borderId="37">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="43">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="23" borderId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="23" borderId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="24" borderId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="44">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="40" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="41" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="42" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1621,28 +1615,25 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1651,7 +1642,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1669,25 +1660,22 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1696,13 +1684,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1717,13 +1705,13 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1753,10 +1741,10 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="19" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="22" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1765,22 +1753,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="19" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="19" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="6" fillId="13" borderId="9" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="6" fillId="4" borderId="10" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1789,7 +1777,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1804,43 +1792,43 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="15" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1858,50 +1846,50 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="28" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1919,103 +1907,103 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="30" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="22" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="17" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="17" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="29" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="30" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="17" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="17" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="21" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="29" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="30" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="29" fillId="7" borderId="10" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="28" fillId="7" borderId="10" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="30" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="5" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="28" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="28" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="9" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="9" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="9" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="9" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="34" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="34" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="35" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="25" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="25" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="28" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="12" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="28" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="26" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="26" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2459,10 +2447,10 @@
       <c r="AH1" s="10">
         <v>30</v>
       </c>
-      <c r="AI1" s="113">
+      <c r="AI1" s="111">
         <v>31</v>
       </c>
-      <c r="AJ1" s="114" t="s">
+      <c r="AJ1" s="112" t="s">
         <v>1</v>
       </c>
       <c r="AK1" s="2"/>
@@ -2488,16 +2476,16 @@
       <c r="H2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="91" t="s">
+      <c r="J2" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="91" t="s">
+      <c r="K2" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="91" t="s">
+      <c r="L2" s="89" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="17" t="s">
@@ -2539,7 +2527,7 @@
       <c r="Y2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="91" t="s">
+      <c r="Z2" s="89" t="s">
         <v>4</v>
       </c>
       <c r="AA2" s="17" t="s">
@@ -2569,8 +2557,8 @@
       <c r="AI2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="115"/>
-      <c r="AL2" s="116" t="s">
+      <c r="AJ2" s="113"/>
+      <c r="AL2" s="114" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2596,9 +2584,9 @@
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
       <c r="Q3" s="23"/>
       <c r="R3" s="23"/>
       <c r="S3" s="23"/>
@@ -2610,7 +2598,7 @@
       <c r="Y3" s="23"/>
       <c r="Z3" s="23"/>
       <c r="AA3" s="24"/>
-      <c r="AB3" s="48"/>
+      <c r="AB3" s="47"/>
       <c r="AC3" s="23"/>
       <c r="AD3" s="23"/>
       <c r="AE3" s="23"/>
@@ -2618,22 +2606,22 @@
       <c r="AG3" s="23"/>
       <c r="AH3" s="23"/>
       <c r="AI3" s="23"/>
-      <c r="AJ3" s="117">
+      <c r="AJ3" s="115">
         <f>SUM(E4:AI4)-SUM(E3:AI3)</f>
         <v>0</v>
       </c>
       <c r="AK3" s="2"/>
-      <c r="AL3" s="118" t="s">
+      <c r="AL3" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="AM3" s="119" t="s">
+      <c r="AM3" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="AN3" s="118" t="s">
+      <c r="AN3" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="AO3" s="139"/>
-      <c r="AP3" s="129"/>
+      <c r="AO3" s="137"/>
+      <c r="AP3" s="127"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:41">
       <c r="A4" s="25"/>
@@ -2651,9 +2639,9 @@
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
       <c r="S4" s="23"/>
@@ -2665,7 +2653,7 @@
       <c r="Y4" s="23"/>
       <c r="Z4" s="23"/>
       <c r="AA4" s="24"/>
-      <c r="AB4" s="48"/>
+      <c r="AB4" s="47"/>
       <c r="AC4" s="23"/>
       <c r="AD4" s="23"/>
       <c r="AE4" s="23"/>
@@ -2673,12 +2661,12 @@
       <c r="AG4" s="23"/>
       <c r="AH4" s="23"/>
       <c r="AI4" s="23"/>
-      <c r="AJ4" s="120"/>
+      <c r="AJ4" s="118"/>
       <c r="AK4" s="2"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="123"/>
-      <c r="AO4" s="128"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="126"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:40">
       <c r="A5" s="28">
@@ -2697,7 +2685,7 @@
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="92"/>
+      <c r="I5" s="90"/>
       <c r="J5" s="32"/>
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
@@ -2705,33 +2693,33 @@
       <c r="N5" s="32"/>
       <c r="O5" s="32"/>
       <c r="P5" s="32"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="60"/>
-      <c r="X5" s="60"/>
-      <c r="Y5" s="60"/>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="60"/>
-      <c r="AB5" s="60"/>
-      <c r="AC5" s="60"/>
-      <c r="AD5" s="60"/>
-      <c r="AE5" s="60"/>
-      <c r="AF5" s="60"/>
-      <c r="AG5" s="60"/>
-      <c r="AH5" s="60"/>
-      <c r="AI5" s="60"/>
-      <c r="AJ5" s="117">
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="58"/>
+      <c r="Y5" s="58"/>
+      <c r="Z5" s="58"/>
+      <c r="AA5" s="58"/>
+      <c r="AB5" s="58"/>
+      <c r="AC5" s="58"/>
+      <c r="AD5" s="58"/>
+      <c r="AE5" s="58"/>
+      <c r="AF5" s="58"/>
+      <c r="AG5" s="58"/>
+      <c r="AH5" s="58"/>
+      <c r="AI5" s="58"/>
+      <c r="AJ5" s="115">
         <f>SUM(E6:AI6)-SUM(E5:AI5)</f>
         <v>0</v>
       </c>
       <c r="AK5" s="2"/>
-      <c r="AL5" s="124"/>
-      <c r="AM5" s="122"/>
-      <c r="AN5" s="123"/>
+      <c r="AL5" s="122"/>
+      <c r="AM5" s="120"/>
+      <c r="AN5" s="121"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:41">
       <c r="A6" s="25"/>
@@ -2744,7 +2732,7 @@
       <c r="F6" s="33"/>
       <c r="G6" s="34"/>
       <c r="H6" s="34"/>
-      <c r="I6" s="92"/>
+      <c r="I6" s="90"/>
       <c r="J6" s="34"/>
       <c r="K6" s="34"/>
       <c r="L6" s="34"/>
@@ -2752,31 +2740,31 @@
       <c r="N6" s="34"/>
       <c r="O6" s="34"/>
       <c r="P6" s="34"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="102"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="60"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60"/>
-      <c r="AC6" s="60"/>
-      <c r="AD6" s="60"/>
-      <c r="AE6" s="60"/>
-      <c r="AF6" s="60"/>
-      <c r="AG6" s="60"/>
-      <c r="AH6" s="60"/>
-      <c r="AI6" s="60"/>
-      <c r="AJ6" s="120"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="58"/>
+      <c r="Y6" s="58"/>
+      <c r="Z6" s="58"/>
+      <c r="AA6" s="58"/>
+      <c r="AB6" s="58"/>
+      <c r="AC6" s="58"/>
+      <c r="AD6" s="58"/>
+      <c r="AE6" s="58"/>
+      <c r="AF6" s="58"/>
+      <c r="AG6" s="58"/>
+      <c r="AH6" s="58"/>
+      <c r="AI6" s="58"/>
+      <c r="AJ6" s="118"/>
       <c r="AK6" s="2"/>
-      <c r="AL6" s="125"/>
-      <c r="AM6" s="122"/>
-      <c r="AN6" s="123"/>
-      <c r="AO6" s="128"/>
+      <c r="AL6" s="123"/>
+      <c r="AM6" s="120"/>
+      <c r="AN6" s="121"/>
+      <c r="AO6" s="126"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:40">
       <c r="A7" s="19">
@@ -2822,14 +2810,14 @@
       <c r="AG7" s="23"/>
       <c r="AH7" s="23"/>
       <c r="AI7" s="23"/>
-      <c r="AJ7" s="117">
+      <c r="AJ7" s="115">
         <f>SUM(E8:AI8)-SUM(E7:AI7)</f>
         <v>0</v>
       </c>
       <c r="AK7" s="2"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="122"/>
-      <c r="AN7" s="126"/>
+      <c r="AL7" s="122"/>
+      <c r="AM7" s="120"/>
+      <c r="AN7" s="124"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:41">
       <c r="A8" s="25"/>
@@ -2838,7 +2826,7 @@
       <c r="D8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="38"/>
+      <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
@@ -2869,24 +2857,24 @@
       <c r="AG8" s="23"/>
       <c r="AH8" s="23"/>
       <c r="AI8" s="23"/>
-      <c r="AJ8" s="120"/>
+      <c r="AJ8" s="118"/>
       <c r="AK8" s="2"/>
-      <c r="AL8" s="125"/>
-      <c r="AM8" s="122"/>
-      <c r="AN8" s="123"/>
-      <c r="AO8" s="128"/>
+      <c r="AL8" s="123"/>
+      <c r="AM8" s="120"/>
+      <c r="AN8" s="121"/>
+      <c r="AO8" s="126"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:40">
       <c r="A9" s="28">
         <v>4</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="40" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="32"/>
@@ -2894,45 +2882,45 @@
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
-      <c r="J9" s="93"/>
+      <c r="J9" s="91"/>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
       <c r="M9" s="32"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="95"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="93"/>
       <c r="P9" s="32"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="60"/>
-      <c r="AE9" s="60"/>
-      <c r="AF9" s="60"/>
-      <c r="AH9" s="60"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="117">
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="101"/>
+      <c r="V9" s="58"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="58"/>
+      <c r="Y9" s="58"/>
+      <c r="Z9" s="58"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="58"/>
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="58"/>
+      <c r="AH9" s="58"/>
+      <c r="AI9" s="58"/>
+      <c r="AJ9" s="115">
         <f>SUM(E10:AI10)-SUM(E9:AI9)</f>
         <v>0</v>
       </c>
       <c r="AK9" s="2"/>
-      <c r="AL9" s="125"/>
-      <c r="AM9" s="122"/>
-      <c r="AN9" s="126"/>
+      <c r="AL9" s="123"/>
+      <c r="AM9" s="120"/>
+      <c r="AN9" s="124"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:42">
       <c r="A10" s="25"/>
       <c r="B10" s="26"/>
       <c r="C10" s="27"/>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="34"/>
@@ -2944,35 +2932,35 @@
       <c r="K10" s="34"/>
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="95"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="93"/>
       <c r="P10" s="34"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="60"/>
-      <c r="AC10" s="60"/>
-      <c r="AD10" s="60"/>
-      <c r="AE10" s="60"/>
-      <c r="AF10" s="60"/>
-      <c r="AG10" s="60"/>
-      <c r="AH10" s="60"/>
-      <c r="AI10" s="60"/>
-      <c r="AJ10" s="120"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="58"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="58"/>
+      <c r="W10" s="58"/>
+      <c r="X10" s="58"/>
+      <c r="Y10" s="58"/>
+      <c r="Z10" s="58"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="58"/>
+      <c r="AC10" s="58"/>
+      <c r="AD10" s="58"/>
+      <c r="AE10" s="58"/>
+      <c r="AF10" s="58"/>
+      <c r="AG10" s="58"/>
+      <c r="AH10" s="58"/>
+      <c r="AI10" s="58"/>
+      <c r="AJ10" s="118"/>
       <c r="AK10" s="2"/>
-      <c r="AL10" s="125"/>
-      <c r="AM10" s="122"/>
-      <c r="AN10" s="123"/>
-      <c r="AO10" s="128"/>
-      <c r="AP10" s="128"/>
+      <c r="AL10" s="123"/>
+      <c r="AM10" s="120"/>
+      <c r="AN10" s="121"/>
+      <c r="AO10" s="126"/>
+      <c r="AP10" s="126"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:40">
       <c r="A11" s="19">
@@ -2981,13 +2969,13 @@
       <c r="B11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="41" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="43"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
@@ -3008,7 +2996,7 @@
       <c r="W11" s="23"/>
       <c r="X11" s="23"/>
       <c r="Y11" s="23"/>
-      <c r="Z11" s="109"/>
+      <c r="Z11" s="107"/>
       <c r="AA11" s="23"/>
       <c r="AB11" s="23"/>
       <c r="AC11" s="23"/>
@@ -3018,14 +3006,14 @@
       <c r="AG11" s="23"/>
       <c r="AH11" s="23"/>
       <c r="AI11" s="23"/>
-      <c r="AJ11" s="117">
+      <c r="AJ11" s="115">
         <f>SUM(E12:AI12)-SUM(E11:AI11)</f>
         <v>0</v>
       </c>
       <c r="AK11" s="2"/>
-      <c r="AL11" s="125"/>
-      <c r="AM11" s="122"/>
-      <c r="AN11" s="126"/>
+      <c r="AL11" s="123"/>
+      <c r="AM11" s="120"/>
+      <c r="AN11" s="124"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:42">
       <c r="A12" s="25"/>
@@ -3055,7 +3043,7 @@
       <c r="W12" s="23"/>
       <c r="X12" s="23"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="109"/>
+      <c r="Z12" s="107"/>
       <c r="AA12" s="23"/>
       <c r="AB12" s="23"/>
       <c r="AC12" s="23"/>
@@ -3065,13 +3053,13 @@
       <c r="AG12" s="23"/>
       <c r="AH12" s="23"/>
       <c r="AI12" s="23"/>
-      <c r="AJ12" s="120"/>
+      <c r="AJ12" s="118"/>
       <c r="AK12" s="2"/>
-      <c r="AL12" s="125"/>
-      <c r="AM12" s="122"/>
-      <c r="AN12" s="123"/>
-      <c r="AO12" s="140"/>
-      <c r="AP12" s="128"/>
+      <c r="AL12" s="123"/>
+      <c r="AM12" s="120"/>
+      <c r="AN12" s="121"/>
+      <c r="AO12" s="138"/>
+      <c r="AP12" s="126"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:41">
       <c r="A13" s="28">
@@ -3080,108 +3068,108 @@
       <c r="B13" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="60"/>
-      <c r="Y13" s="105"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="60"/>
-      <c r="AB13" s="111"/>
-      <c r="AC13" s="111"/>
-      <c r="AD13" s="60"/>
-      <c r="AE13" s="60"/>
-      <c r="AF13" s="60"/>
-      <c r="AG13" s="60"/>
-      <c r="AH13" s="60"/>
-      <c r="AI13" s="60"/>
-      <c r="AJ13" s="117">
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="58"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="58"/>
+      <c r="Y13" s="103"/>
+      <c r="Z13" s="108"/>
+      <c r="AA13" s="58"/>
+      <c r="AB13" s="109"/>
+      <c r="AC13" s="109"/>
+      <c r="AD13" s="58"/>
+      <c r="AE13" s="58"/>
+      <c r="AF13" s="58"/>
+      <c r="AG13" s="58"/>
+      <c r="AH13" s="58"/>
+      <c r="AI13" s="58"/>
+      <c r="AJ13" s="115">
         <f>SUM(E14:AI14)-SUM(E13:AI13)</f>
         <v>0</v>
       </c>
       <c r="AK13" s="2"/>
-      <c r="AL13" s="125"/>
-      <c r="AM13" s="122"/>
-      <c r="AN13" s="126"/>
-      <c r="AO13" s="128"/>
+      <c r="AL13" s="123"/>
+      <c r="AM13" s="120"/>
+      <c r="AN13" s="124"/>
+      <c r="AO13" s="126"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:44">
       <c r="A14" s="25"/>
       <c r="B14" s="26"/>
       <c r="C14" s="27"/>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="104"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="60"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="60"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="60"/>
-      <c r="AE14" s="60"/>
-      <c r="AF14" s="60"/>
-      <c r="AG14" s="60"/>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="60"/>
-      <c r="AJ14" s="120"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="58"/>
+      <c r="V14" s="58"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="58"/>
+      <c r="Y14" s="58"/>
+      <c r="Z14" s="58"/>
+      <c r="AA14" s="58"/>
+      <c r="AB14" s="58"/>
+      <c r="AC14" s="58"/>
+      <c r="AE14" s="58"/>
+      <c r="AF14" s="58"/>
+      <c r="AG14" s="58"/>
+      <c r="AH14" s="58"/>
+      <c r="AI14" s="58"/>
+      <c r="AJ14" s="118"/>
       <c r="AK14" s="2"/>
-      <c r="AL14" s="125"/>
-      <c r="AM14" s="122"/>
-      <c r="AN14" s="123"/>
-      <c r="AO14" s="140"/>
-      <c r="AP14" s="128"/>
-      <c r="AQ14" s="128"/>
-      <c r="AR14" s="128"/>
+      <c r="AL14" s="123"/>
+      <c r="AM14" s="120"/>
+      <c r="AN14" s="121"/>
+      <c r="AO14" s="138"/>
+      <c r="AP14" s="126"/>
+      <c r="AQ14" s="126"/>
+      <c r="AR14" s="126"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:40">
       <c r="A15" s="19">
         <v>7</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="22" t="s">
@@ -3189,7 +3177,7 @@
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
-      <c r="G15" s="48"/>
+      <c r="G15" s="47"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -3202,8 +3190,8 @@
       <c r="Q15" s="24"/>
       <c r="R15" s="24"/>
       <c r="S15" s="24"/>
-      <c r="T15" s="100"/>
-      <c r="U15" s="100"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="98"/>
       <c r="V15" s="23"/>
       <c r="W15" s="23"/>
       <c r="X15" s="23"/>
@@ -3218,14 +3206,14 @@
       <c r="AG15" s="23"/>
       <c r="AH15" s="23"/>
       <c r="AI15" s="23"/>
-      <c r="AJ15" s="117">
+      <c r="AJ15" s="115">
         <f>SUM(E16:AI16)-SUM(E15:AI15)</f>
         <v>0</v>
       </c>
       <c r="AK15" s="2"/>
-      <c r="AL15" s="125"/>
-      <c r="AM15" s="122"/>
-      <c r="AN15" s="126"/>
+      <c r="AL15" s="123"/>
+      <c r="AM15" s="120"/>
+      <c r="AN15" s="124"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:43">
       <c r="A16" s="25"/>
@@ -3236,7 +3224,7 @@
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="48"/>
+      <c r="G16" s="47"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -3249,8 +3237,8 @@
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="24"/>
-      <c r="T16" s="100"/>
-      <c r="U16" s="100"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="98"/>
       <c r="V16" s="23"/>
       <c r="W16" s="23"/>
       <c r="X16" s="23"/>
@@ -3265,130 +3253,130 @@
       <c r="AG16" s="23"/>
       <c r="AH16" s="23"/>
       <c r="AI16" s="23"/>
-      <c r="AJ16" s="120"/>
+      <c r="AJ16" s="118"/>
       <c r="AK16" s="2"/>
-      <c r="AL16" s="125"/>
-      <c r="AM16" s="122"/>
-      <c r="AN16" s="122"/>
-      <c r="AO16" s="140"/>
-      <c r="AP16" s="128"/>
-      <c r="AQ16" s="128"/>
+      <c r="AL16" s="123"/>
+      <c r="AM16" s="120"/>
+      <c r="AN16" s="120"/>
+      <c r="AO16" s="138"/>
+      <c r="AP16" s="126"/>
+      <c r="AQ16" s="126"/>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:40">
       <c r="A17" s="28">
         <v>8</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="40" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="50"/>
+      <c r="G17" s="49"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
       <c r="M17" s="32"/>
       <c r="N17" s="32"/>
       <c r="O17" s="32"/>
       <c r="P17" s="32"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="105"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="45"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="45"/>
-      <c r="Y17" s="45"/>
-      <c r="Z17" s="107"/>
-      <c r="AA17" s="107"/>
-      <c r="AB17" s="45"/>
-      <c r="AC17" s="45"/>
-      <c r="AD17" s="45"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="127"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="117">
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="103"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="104"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="44"/>
+      <c r="Z17" s="105"/>
+      <c r="AA17" s="105"/>
+      <c r="AB17" s="44"/>
+      <c r="AC17" s="44"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="44"/>
+      <c r="AF17" s="44"/>
+      <c r="AG17" s="125"/>
+      <c r="AH17" s="58"/>
+      <c r="AI17" s="58"/>
+      <c r="AJ17" s="115">
         <f>SUM(E18:AI18)-SUM(E17:AI17)</f>
         <v>0</v>
       </c>
       <c r="AK17" s="2"/>
-      <c r="AL17" s="125"/>
-      <c r="AM17" s="122"/>
-      <c r="AN17" s="126"/>
+      <c r="AL17" s="123"/>
+      <c r="AM17" s="120"/>
+      <c r="AN17" s="124"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:41">
       <c r="A18" s="25"/>
       <c r="B18" s="26"/>
       <c r="C18" s="27"/>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="34"/>
-      <c r="G18" s="51"/>
+      <c r="G18" s="50"/>
       <c r="H18" s="34"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
       <c r="M18" s="34"/>
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="105"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="45"/>
-      <c r="Y18" s="45"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="107"/>
-      <c r="AB18" s="45"/>
-      <c r="AC18" s="45"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="68"/>
-      <c r="AF18" s="45"/>
-      <c r="AG18" s="107"/>
-      <c r="AH18" s="60"/>
-      <c r="AI18" s="60"/>
-      <c r="AJ18" s="120"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="58"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="44"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="44"/>
+      <c r="Z18" s="110"/>
+      <c r="AA18" s="105"/>
+      <c r="AB18" s="44"/>
+      <c r="AC18" s="44"/>
+      <c r="AD18" s="44"/>
+      <c r="AE18" s="66"/>
+      <c r="AF18" s="44"/>
+      <c r="AG18" s="105"/>
+      <c r="AH18" s="58"/>
+      <c r="AI18" s="58"/>
+      <c r="AJ18" s="118"/>
       <c r="AK18" s="2"/>
-      <c r="AL18" s="125"/>
-      <c r="AM18" s="122"/>
-      <c r="AN18" s="125"/>
-      <c r="AO18" s="128"/>
+      <c r="AL18" s="123"/>
+      <c r="AM18" s="120"/>
+      <c r="AN18" s="123"/>
+      <c r="AO18" s="126"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:40">
       <c r="A19" s="19">
         <v>9</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="23"/>
-      <c r="F19" s="52"/>
+      <c r="F19" s="51"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="52"/>
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
       <c r="K19" s="23"/>
@@ -3396,7 +3384,7 @@
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
-      <c r="P19" s="100"/>
+      <c r="P19" s="98"/>
       <c r="Q19" s="23"/>
       <c r="R19" s="23"/>
       <c r="S19" s="23"/>
@@ -3416,14 +3404,14 @@
       <c r="AG19" s="23"/>
       <c r="AH19" s="23"/>
       <c r="AI19" s="23"/>
-      <c r="AJ19" s="117">
+      <c r="AJ19" s="115">
         <f>SUM(E20:AI20)-SUM(E19:AI19)</f>
         <v>0</v>
       </c>
       <c r="AK19" s="2"/>
-      <c r="AL19" s="128"/>
-      <c r="AM19" s="122"/>
-      <c r="AN19" s="126"/>
+      <c r="AL19" s="126"/>
+      <c r="AM19" s="120"/>
+      <c r="AN19" s="124"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:41">
       <c r="A20" s="25"/>
@@ -3433,9 +3421,9 @@
         <v>18</v>
       </c>
       <c r="E20" s="23"/>
-      <c r="F20" s="48"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="23"/>
-      <c r="H20" s="54"/>
+      <c r="H20" s="53"/>
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
       <c r="K20" s="23"/>
@@ -3443,7 +3431,7 @@
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
-      <c r="P20" s="100"/>
+      <c r="P20" s="98"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
       <c r="S20" s="23"/>
@@ -3463,117 +3451,117 @@
       <c r="AG20" s="23"/>
       <c r="AH20" s="23"/>
       <c r="AI20" s="23"/>
-      <c r="AJ20" s="120"/>
+      <c r="AJ20" s="118"/>
       <c r="AK20" s="2"/>
-      <c r="AL20" s="129"/>
-      <c r="AM20" s="122"/>
-      <c r="AN20" s="123"/>
-      <c r="AO20" s="128"/>
+      <c r="AL20" s="127"/>
+      <c r="AM20" s="120"/>
+      <c r="AN20" s="121"/>
+      <c r="AO20" s="126"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:40">
       <c r="A21" s="28">
         <v>10</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="D21" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="45"/>
-      <c r="Y21" s="105"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="111"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="60"/>
-      <c r="AE21" s="60"/>
-      <c r="AF21" s="60"/>
-      <c r="AG21" s="60"/>
-      <c r="AH21" s="60"/>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="117">
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="105"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="44"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="103"/>
+      <c r="Z21" s="58"/>
+      <c r="AA21" s="58"/>
+      <c r="AB21" s="109"/>
+      <c r="AC21" s="109"/>
+      <c r="AD21" s="58"/>
+      <c r="AE21" s="58"/>
+      <c r="AF21" s="58"/>
+      <c r="AG21" s="58"/>
+      <c r="AH21" s="58"/>
+      <c r="AI21" s="58"/>
+      <c r="AJ21" s="115">
         <f>SUM(E22:AI22)-SUM(E21:AI21)</f>
         <v>0</v>
       </c>
       <c r="AK21" s="2"/>
       <c r="AL21" s="1"/>
-      <c r="AM21" s="123"/>
-      <c r="AN21" s="126"/>
+      <c r="AM21" s="121"/>
+      <c r="AN21" s="124"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:40">
       <c r="A22" s="25"/>
       <c r="B22" s="26"/>
       <c r="C22" s="27"/>
-      <c r="D22" s="56" t="s">
+      <c r="D22" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="45"/>
-      <c r="V22" s="45"/>
-      <c r="W22" s="45"/>
-      <c r="X22" s="45"/>
-      <c r="Y22" s="105"/>
-      <c r="Z22" s="60"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="60"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="60"/>
-      <c r="AI22" s="60"/>
-      <c r="AJ22" s="120"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="103"/>
+      <c r="Z22" s="58"/>
+      <c r="AA22" s="58"/>
+      <c r="AB22" s="58"/>
+      <c r="AC22" s="58"/>
+      <c r="AD22" s="58"/>
+      <c r="AF22" s="58"/>
+      <c r="AG22" s="58"/>
+      <c r="AH22" s="58"/>
+      <c r="AI22" s="58"/>
+      <c r="AJ22" s="118"/>
       <c r="AK22" s="2"/>
-      <c r="AL22" s="125"/>
-      <c r="AM22" s="125"/>
-      <c r="AN22" s="123"/>
+      <c r="AL22" s="123"/>
+      <c r="AM22" s="123"/>
+      <c r="AN22" s="121"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:40">
       <c r="A23" s="19">
         <v>11</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="57" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="22" t="s">
@@ -3581,7 +3569,7 @@
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
-      <c r="G23" s="48"/>
+      <c r="G23" s="47"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
@@ -3610,14 +3598,14 @@
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
       <c r="AI23" s="23"/>
-      <c r="AJ23" s="117">
+      <c r="AJ23" s="115">
         <f>SUM(E24:AI24)-SUM(E23:AI23)</f>
         <v>0</v>
       </c>
       <c r="AK23" s="2"/>
-      <c r="AL23" s="125"/>
-      <c r="AM23" s="123"/>
-      <c r="AN23" s="126"/>
+      <c r="AL23" s="123"/>
+      <c r="AM23" s="121"/>
+      <c r="AN23" s="124"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:40">
       <c r="A24" s="25"/>
@@ -3628,7 +3616,7 @@
       </c>
       <c r="E24" s="23"/>
       <c r="F24" s="23"/>
-      <c r="G24" s="48"/>
+      <c r="G24" s="47"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
@@ -3657,122 +3645,122 @@
       <c r="AG24" s="23"/>
       <c r="AH24" s="23"/>
       <c r="AI24" s="23"/>
-      <c r="AJ24" s="120"/>
+      <c r="AJ24" s="118"/>
       <c r="AK24" s="2"/>
-      <c r="AL24" s="125"/>
-      <c r="AM24" s="125"/>
-      <c r="AN24" s="126"/>
+      <c r="AL24" s="123"/>
+      <c r="AM24" s="123"/>
+      <c r="AN24" s="124"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:40">
       <c r="A25" s="28">
         <v>12</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="60"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="45"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="108"/>
-      <c r="X25" s="45"/>
-      <c r="Y25" s="45"/>
-      <c r="Z25" s="45"/>
-      <c r="AA25" s="45"/>
-      <c r="AB25" s="45"/>
-      <c r="AC25" s="107"/>
-      <c r="AD25" s="45"/>
-      <c r="AE25" s="45"/>
-      <c r="AF25" s="45"/>
-      <c r="AG25" s="130"/>
-      <c r="AH25" s="60"/>
-      <c r="AI25" s="60"/>
-      <c r="AJ25" s="117">
+      <c r="E25" s="58"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="64"/>
+      <c r="W25" s="106"/>
+      <c r="X25" s="44"/>
+      <c r="Y25" s="44"/>
+      <c r="Z25" s="44"/>
+      <c r="AA25" s="44"/>
+      <c r="AB25" s="44"/>
+      <c r="AC25" s="105"/>
+      <c r="AD25" s="44"/>
+      <c r="AE25" s="44"/>
+      <c r="AF25" s="44"/>
+      <c r="AG25" s="128"/>
+      <c r="AH25" s="58"/>
+      <c r="AI25" s="58"/>
+      <c r="AJ25" s="115">
         <f>SUM(E26:AI26)-SUM(E25:AI25)</f>
         <v>0</v>
       </c>
       <c r="AK25" s="2"/>
-      <c r="AL25" s="125"/>
-      <c r="AM25" s="119"/>
-      <c r="AN25" s="126"/>
+      <c r="AL25" s="123"/>
+      <c r="AM25" s="117"/>
+      <c r="AN25" s="124"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:40">
       <c r="A26" s="25"/>
       <c r="B26" s="26"/>
       <c r="C26" s="27"/>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="34"/>
-      <c r="F26" s="51"/>
+      <c r="F26" s="50"/>
       <c r="G26" s="34"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="108"/>
-      <c r="X26" s="45"/>
-      <c r="Y26" s="45"/>
-      <c r="Z26" s="45"/>
-      <c r="AA26" s="45"/>
-      <c r="AB26" s="45"/>
-      <c r="AC26" s="107"/>
-      <c r="AD26" s="45"/>
-      <c r="AE26" s="45"/>
-      <c r="AF26" s="45"/>
-      <c r="AG26" s="60"/>
-      <c r="AH26" s="60"/>
-      <c r="AI26" s="60"/>
-      <c r="AJ26" s="120"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="106"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="105"/>
+      <c r="AD26" s="44"/>
+      <c r="AE26" s="44"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="58"/>
+      <c r="AH26" s="58"/>
+      <c r="AI26" s="58"/>
+      <c r="AJ26" s="118"/>
       <c r="AK26" s="2"/>
-      <c r="AL26" s="125"/>
-      <c r="AM26" s="131"/>
-      <c r="AN26" s="126"/>
+      <c r="AL26" s="123"/>
+      <c r="AM26" s="129"/>
+      <c r="AN26" s="124"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:40">
       <c r="A27" s="28">
         <v>13</v>
       </c>
       <c r="B27" s="20"/>
-      <c r="C27" s="47"/>
+      <c r="C27" s="46"/>
       <c r="D27" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="43"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="42"/>
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
       <c r="K27" s="23"/>
@@ -3800,25 +3788,25 @@
       <c r="AG27" s="23"/>
       <c r="AH27" s="23"/>
       <c r="AI27" s="23"/>
-      <c r="AJ27" s="117">
+      <c r="AJ27" s="115">
         <f>SUM(E28:AI28)-SUM(E27:AI27)</f>
         <v>0</v>
       </c>
       <c r="AK27" s="2"/>
-      <c r="AL27" s="125"/>
-      <c r="AM27" s="123"/>
-      <c r="AN27" s="123"/>
+      <c r="AL27" s="123"/>
+      <c r="AM27" s="121"/>
+      <c r="AN27" s="121"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:40">
       <c r="A28" s="25"/>
       <c r="B28" s="26"/>
       <c r="C28" s="27"/>
-      <c r="D28" s="62" t="s">
+      <c r="D28" s="60" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="24"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
       <c r="J28" s="24"/>
@@ -3847,117 +3835,117 @@
       <c r="AG28" s="24"/>
       <c r="AH28" s="24"/>
       <c r="AI28" s="24"/>
-      <c r="AJ28" s="120"/>
+      <c r="AJ28" s="118"/>
       <c r="AK28" s="2"/>
-      <c r="AL28" s="125"/>
-      <c r="AM28" s="125"/>
-      <c r="AN28" s="123"/>
+      <c r="AL28" s="123"/>
+      <c r="AM28" s="123"/>
+      <c r="AN28" s="121"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:40">
       <c r="A29" s="28">
         <v>14</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="64" t="s">
+      <c r="B29" s="48"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="66"/>
-      <c r="V29" s="66"/>
-      <c r="W29" s="66"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="66"/>
-      <c r="Z29" s="66"/>
-      <c r="AA29" s="66"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="66"/>
-      <c r="AD29" s="66"/>
-      <c r="AE29" s="66"/>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="66"/>
-      <c r="AH29" s="66"/>
-      <c r="AI29" s="66"/>
-      <c r="AJ29" s="117">
+      <c r="E29" s="63"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="64"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="64"/>
+      <c r="AB29" s="64"/>
+      <c r="AC29" s="64"/>
+      <c r="AD29" s="64"/>
+      <c r="AE29" s="64"/>
+      <c r="AF29" s="64"/>
+      <c r="AG29" s="64"/>
+      <c r="AH29" s="64"/>
+      <c r="AI29" s="64"/>
+      <c r="AJ29" s="115">
         <f>SUM(E30:AI30)-SUM(E29:AI29)</f>
         <v>0</v>
       </c>
       <c r="AK29" s="2"/>
-      <c r="AL29" s="125"/>
-      <c r="AM29" s="123"/>
-      <c r="AN29" s="123"/>
+      <c r="AL29" s="123"/>
+      <c r="AM29" s="121"/>
+      <c r="AN29" s="121"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:40">
       <c r="A30" s="25"/>
       <c r="B30" s="26"/>
       <c r="C30" s="27"/>
-      <c r="D30" s="67" t="s">
+      <c r="D30" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="101"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
-      <c r="X30" s="45"/>
-      <c r="Y30" s="45"/>
-      <c r="Z30" s="45"/>
-      <c r="AA30" s="45"/>
-      <c r="AB30" s="45"/>
-      <c r="AC30" s="45"/>
-      <c r="AD30" s="45"/>
-      <c r="AE30" s="45"/>
-      <c r="AF30" s="45"/>
-      <c r="AG30" s="45"/>
-      <c r="AH30" s="45"/>
-      <c r="AI30" s="45"/>
-      <c r="AJ30" s="120"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="44"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="44"/>
+      <c r="AB30" s="44"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="44"/>
+      <c r="AE30" s="44"/>
+      <c r="AF30" s="44"/>
+      <c r="AG30" s="44"/>
+      <c r="AH30" s="44"/>
+      <c r="AI30" s="44"/>
+      <c r="AJ30" s="118"/>
       <c r="AK30" s="2"/>
-      <c r="AL30" s="125"/>
-      <c r="AM30" s="125"/>
-      <c r="AN30" s="123"/>
+      <c r="AL30" s="123"/>
+      <c r="AM30" s="123"/>
+      <c r="AN30" s="121"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:40">
       <c r="A31" s="28">
         <v>15</v>
       </c>
       <c r="B31" s="20"/>
-      <c r="C31" s="69"/>
+      <c r="C31" s="67"/>
       <c r="D31" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
@@ -3986,25 +3974,25 @@
       <c r="AG31" s="23"/>
       <c r="AH31" s="23"/>
       <c r="AI31" s="23"/>
-      <c r="AJ31" s="117">
+      <c r="AJ31" s="115">
         <f>SUM(E32:AI32)-SUM(E31:AI31)</f>
         <v>0</v>
       </c>
       <c r="AK31" s="2"/>
-      <c r="AL31" s="132"/>
-      <c r="AM31" s="123"/>
-      <c r="AN31" s="123"/>
+      <c r="AL31" s="130"/>
+      <c r="AM31" s="121"/>
+      <c r="AN31" s="121"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" spans="1:40">
       <c r="A32" s="25"/>
       <c r="B32" s="26"/>
       <c r="C32" s="27"/>
-      <c r="D32" s="62" t="s">
+      <c r="D32" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
@@ -4033,108 +4021,108 @@
       <c r="AG32" s="23"/>
       <c r="AH32" s="23"/>
       <c r="AI32" s="23"/>
-      <c r="AJ32" s="120"/>
+      <c r="AJ32" s="118"/>
       <c r="AK32" s="2"/>
-      <c r="AL32" s="125"/>
-      <c r="AM32" s="125"/>
-      <c r="AN32" s="123"/>
+      <c r="AL32" s="123"/>
+      <c r="AM32" s="123"/>
+      <c r="AN32" s="121"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:40">
       <c r="A33" s="19"/>
-      <c r="B33" s="70"/>
+      <c r="B33" s="68"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="45"/>
-      <c r="AC33" s="45"/>
-      <c r="AD33" s="45"/>
-      <c r="AE33" s="45"/>
-      <c r="AF33" s="45"/>
-      <c r="AG33" s="45"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="45"/>
-      <c r="AJ33" s="117"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="44"/>
+      <c r="AB33" s="44"/>
+      <c r="AC33" s="44"/>
+      <c r="AD33" s="44"/>
+      <c r="AE33" s="44"/>
+      <c r="AF33" s="44"/>
+      <c r="AG33" s="44"/>
+      <c r="AH33" s="44"/>
+      <c r="AI33" s="44"/>
+      <c r="AJ33" s="115"/>
       <c r="AK33" s="2"/>
-      <c r="AL33" s="132"/>
-      <c r="AM33" s="123"/>
-      <c r="AN33" s="123"/>
+      <c r="AL33" s="130"/>
+      <c r="AM33" s="121"/>
+      <c r="AN33" s="121"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:40">
       <c r="A34" s="19"/>
       <c r="B34" s="26"/>
       <c r="C34" s="27"/>
-      <c r="D34" s="71" t="s">
+      <c r="D34" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="45"/>
-      <c r="AB34" s="45"/>
-      <c r="AC34" s="45"/>
-      <c r="AD34" s="45"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="45"/>
-      <c r="AJ34" s="120"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="44"/>
+      <c r="Y34" s="44"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="44"/>
+      <c r="AB34" s="44"/>
+      <c r="AC34" s="44"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="44"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="44"/>
+      <c r="AH34" s="44"/>
+      <c r="AI34" s="44"/>
+      <c r="AJ34" s="118"/>
       <c r="AK34" s="2"/>
-      <c r="AL34" s="125"/>
-      <c r="AM34" s="125"/>
-      <c r="AN34" s="123"/>
+      <c r="AL34" s="123"/>
+      <c r="AM34" s="123"/>
+      <c r="AN34" s="121"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:40">
       <c r="A35" s="19"/>
-      <c r="B35" s="73"/>
-      <c r="C35" s="74"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="72"/>
       <c r="D35" s="22"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
@@ -4163,20 +4151,20 @@
       <c r="AG35" s="23"/>
       <c r="AH35" s="23"/>
       <c r="AI35" s="23"/>
-      <c r="AJ35" s="117"/>
+      <c r="AJ35" s="115"/>
       <c r="AK35" s="2"/>
-      <c r="AL35" s="132"/>
-      <c r="AM35" s="123"/>
-      <c r="AN35" s="123"/>
+      <c r="AL35" s="130"/>
+      <c r="AM35" s="121"/>
+      <c r="AN35" s="121"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:40">
       <c r="A36" s="19"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="76"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="74"/>
       <c r="D36" s="22"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
@@ -4205,104 +4193,104 @@
       <c r="AG36" s="23"/>
       <c r="AH36" s="23"/>
       <c r="AI36" s="23"/>
-      <c r="AJ36" s="120"/>
+      <c r="AJ36" s="118"/>
       <c r="AK36" s="2"/>
-      <c r="AL36" s="125"/>
-      <c r="AM36" s="125"/>
-      <c r="AN36" s="123"/>
+      <c r="AL36" s="123"/>
+      <c r="AM36" s="123"/>
+      <c r="AN36" s="121"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" spans="1:40">
       <c r="A37" s="19"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="45"/>
-      <c r="V37" s="45"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="45"/>
-      <c r="AB37" s="45"/>
-      <c r="AC37" s="45"/>
-      <c r="AD37" s="45"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="45"/>
-      <c r="AJ37" s="117"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="44"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="44"/>
+      <c r="AB37" s="44"/>
+      <c r="AC37" s="44"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="44"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="44"/>
+      <c r="AH37" s="44"/>
+      <c r="AI37" s="44"/>
+      <c r="AJ37" s="115"/>
       <c r="AK37" s="2"/>
-      <c r="AL37" s="132"/>
-      <c r="AM37" s="123"/>
-      <c r="AN37" s="123"/>
+      <c r="AL37" s="130"/>
+      <c r="AM37" s="121"/>
+      <c r="AN37" s="121"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:40">
       <c r="A38" s="19"/>
       <c r="B38" s="26"/>
       <c r="C38" s="27"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="45"/>
-      <c r="R38" s="45"/>
-      <c r="S38" s="45"/>
-      <c r="T38" s="45"/>
-      <c r="U38" s="45"/>
-      <c r="V38" s="45"/>
-      <c r="W38" s="45"/>
-      <c r="X38" s="45"/>
-      <c r="Y38" s="45"/>
-      <c r="Z38" s="45"/>
-      <c r="AA38" s="45"/>
-      <c r="AB38" s="45"/>
-      <c r="AC38" s="45"/>
-      <c r="AD38" s="45"/>
-      <c r="AE38" s="45"/>
-      <c r="AF38" s="45"/>
-      <c r="AG38" s="45"/>
-      <c r="AH38" s="45"/>
-      <c r="AI38" s="45"/>
-      <c r="AJ38" s="120"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="44"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="44"/>
+      <c r="AD38" s="44"/>
+      <c r="AE38" s="44"/>
+      <c r="AF38" s="44"/>
+      <c r="AG38" s="44"/>
+      <c r="AH38" s="44"/>
+      <c r="AI38" s="44"/>
+      <c r="AJ38" s="118"/>
       <c r="AK38" s="2"/>
-      <c r="AL38" s="133"/>
-      <c r="AM38" s="125"/>
-      <c r="AN38" s="123"/>
+      <c r="AL38" s="131"/>
+      <c r="AM38" s="123"/>
+      <c r="AN38" s="121"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:40">
       <c r="A39" s="19"/>
-      <c r="B39" s="73"/>
-      <c r="C39" s="74"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="72"/>
       <c r="D39" s="22"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
@@ -4331,19 +4319,19 @@
       <c r="AG39" s="23"/>
       <c r="AH39" s="23"/>
       <c r="AI39" s="23"/>
-      <c r="AJ39" s="117"/>
+      <c r="AJ39" s="115"/>
       <c r="AK39" s="2"/>
-      <c r="AM39" s="123"/>
-      <c r="AN39" s="123"/>
+      <c r="AM39" s="121"/>
+      <c r="AN39" s="121"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:38">
       <c r="A40" s="19"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="76"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
       <c r="D40" s="22"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
@@ -4372,18 +4360,18 @@
       <c r="AG40" s="23"/>
       <c r="AH40" s="23"/>
       <c r="AI40" s="23"/>
-      <c r="AJ40" s="120"/>
+      <c r="AJ40" s="118"/>
       <c r="AK40" s="2"/>
-      <c r="AL40" s="125"/>
+      <c r="AL40" s="123"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:37">
       <c r="A41" s="19"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="79"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="77"/>
       <c r="D41" s="22"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
@@ -4412,17 +4400,17 @@
       <c r="AG41" s="23"/>
       <c r="AH41" s="23"/>
       <c r="AI41" s="23"/>
-      <c r="AJ41" s="117"/>
+      <c r="AJ41" s="115"/>
       <c r="AK41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:37">
       <c r="A42" s="19"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="79"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="77"/>
       <c r="D42" s="22"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
@@ -4451,17 +4439,17 @@
       <c r="AG42" s="23"/>
       <c r="AH42" s="23"/>
       <c r="AI42" s="23"/>
-      <c r="AJ42" s="120"/>
+      <c r="AJ42" s="118"/>
       <c r="AK42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:37">
       <c r="A43" s="19"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="79"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="77"/>
       <c r="D43" s="22"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
       <c r="H43" s="23"/>
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
@@ -4490,17 +4478,17 @@
       <c r="AG43" s="23"/>
       <c r="AH43" s="23"/>
       <c r="AI43" s="23"/>
-      <c r="AJ43" s="117"/>
+      <c r="AJ43" s="115"/>
       <c r="AK43" s="2"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:37">
       <c r="A44" s="19"/>
-      <c r="B44" s="73"/>
-      <c r="C44" s="74"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="72"/>
       <c r="D44" s="22"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
       <c r="H44" s="23"/>
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
@@ -4529,17 +4517,17 @@
       <c r="AG44" s="23"/>
       <c r="AH44" s="23"/>
       <c r="AI44" s="23"/>
-      <c r="AJ44" s="120"/>
+      <c r="AJ44" s="118"/>
       <c r="AK44" s="2"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:37">
       <c r="A45" s="19"/>
-      <c r="B45" s="73"/>
-      <c r="C45" s="74"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="72"/>
       <c r="D45" s="22"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
       <c r="H45" s="23"/>
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
@@ -4568,17 +4556,17 @@
       <c r="AG45" s="23"/>
       <c r="AH45" s="23"/>
       <c r="AI45" s="23"/>
-      <c r="AJ45" s="117"/>
+      <c r="AJ45" s="115"/>
       <c r="AK45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:37">
       <c r="A46" s="19"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="74"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="72"/>
       <c r="D46" s="22"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
       <c r="H46" s="23"/>
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
@@ -4607,17 +4595,17 @@
       <c r="AG46" s="23"/>
       <c r="AH46" s="23"/>
       <c r="AI46" s="23"/>
-      <c r="AJ46" s="120"/>
+      <c r="AJ46" s="118"/>
       <c r="AK46" s="2"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" spans="1:37">
       <c r="A47" s="19"/>
-      <c r="B47" s="73"/>
-      <c r="C47" s="74"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="72"/>
       <c r="D47" s="22"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
@@ -4646,17 +4634,17 @@
       <c r="AG47" s="23"/>
       <c r="AH47" s="23"/>
       <c r="AI47" s="23"/>
-      <c r="AJ47" s="117"/>
+      <c r="AJ47" s="115"/>
       <c r="AK47" s="2"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:37">
       <c r="A48" s="19"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="80"/>
+      <c r="B48" s="71"/>
+      <c r="C48" s="78"/>
       <c r="D48" s="22"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
       <c r="H48" s="23"/>
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
@@ -4685,15 +4673,15 @@
       <c r="AG48" s="23"/>
       <c r="AH48" s="23"/>
       <c r="AI48" s="23"/>
-      <c r="AJ48" s="120"/>
+      <c r="AJ48" s="118"/>
       <c r="AK48" s="2"/>
     </row>
     <row r="49" ht="24.95" hidden="1" customHeight="1" spans="1:39">
       <c r="A49" s="19">
         <v>13</v>
       </c>
-      <c r="B49" s="73"/>
-      <c r="C49" s="81" t="s">
+      <c r="B49" s="71"/>
+      <c r="C49" s="79" t="s">
         <v>25</v>
       </c>
       <c r="D49" s="22" t="s">
@@ -4730,7 +4718,7 @@
       <c r="AG49" s="23"/>
       <c r="AH49" s="23"/>
       <c r="AI49" s="23"/>
-      <c r="AJ49" s="134"/>
+      <c r="AJ49" s="132"/>
       <c r="AK49" s="2"/>
       <c r="AM49" s="4">
         <f>COUNTIF(E26:AI49,8.5)</f>
@@ -4739,8 +4727,8 @@
     </row>
     <row r="50" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A50" s="25"/>
-      <c r="B50" s="75"/>
-      <c r="C50" s="82"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="80"/>
       <c r="D50" s="22" t="s">
         <v>18</v>
       </c>
@@ -4775,7 +4763,7 @@
       <c r="AG50" s="23"/>
       <c r="AH50" s="23"/>
       <c r="AI50" s="23"/>
-      <c r="AJ50" s="135"/>
+      <c r="AJ50" s="133"/>
       <c r="AK50" s="2"/>
       <c r="AL50" s="3">
         <f>COUNTIF(E50:AI50,22)</f>
@@ -4786,94 +4774,94 @@
       <c r="A51" s="28">
         <v>14</v>
       </c>
-      <c r="B51" s="83"/>
-      <c r="C51" s="81" t="s">
+      <c r="B51" s="81"/>
+      <c r="C51" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="41" t="s">
+      <c r="D51" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="60"/>
-      <c r="F51" s="60"/>
-      <c r="G51" s="60"/>
-      <c r="H51" s="60"/>
-      <c r="I51" s="60"/>
-      <c r="J51" s="60"/>
-      <c r="K51" s="60"/>
-      <c r="L51" s="60"/>
-      <c r="M51" s="60"/>
-      <c r="N51" s="60"/>
-      <c r="O51" s="60"/>
-      <c r="P51" s="60"/>
-      <c r="Q51" s="60"/>
-      <c r="R51" s="60"/>
-      <c r="S51" s="60"/>
-      <c r="T51" s="60"/>
-      <c r="U51" s="60"/>
-      <c r="V51" s="60"/>
-      <c r="W51" s="60"/>
-      <c r="X51" s="60"/>
-      <c r="Y51" s="60"/>
-      <c r="Z51" s="60"/>
-      <c r="AA51" s="60"/>
-      <c r="AB51" s="60"/>
-      <c r="AC51" s="60"/>
-      <c r="AD51" s="60"/>
-      <c r="AE51" s="60"/>
-      <c r="AF51" s="60"/>
-      <c r="AG51" s="60"/>
-      <c r="AH51" s="60"/>
-      <c r="AI51" s="60"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
+      <c r="K51" s="58"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="58"/>
+      <c r="S51" s="58"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="58"/>
+      <c r="V51" s="58"/>
+      <c r="W51" s="58"/>
+      <c r="X51" s="58"/>
+      <c r="Y51" s="58"/>
+      <c r="Z51" s="58"/>
+      <c r="AA51" s="58"/>
+      <c r="AB51" s="58"/>
+      <c r="AC51" s="58"/>
+      <c r="AD51" s="58"/>
+      <c r="AE51" s="58"/>
+      <c r="AF51" s="58"/>
+      <c r="AG51" s="58"/>
+      <c r="AH51" s="58"/>
+      <c r="AI51" s="58"/>
       <c r="AJ51" s="7"/>
       <c r="AK51" s="2"/>
     </row>
     <row r="52" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A52" s="25"/>
-      <c r="B52" s="75"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="41" t="s">
+      <c r="B52" s="73"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="60"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="60"/>
-      <c r="H52" s="60"/>
-      <c r="I52" s="60"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="60"/>
-      <c r="L52" s="60"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="60"/>
-      <c r="O52" s="60"/>
-      <c r="P52" s="60"/>
-      <c r="Q52" s="60"/>
-      <c r="R52" s="60"/>
-      <c r="S52" s="60"/>
-      <c r="T52" s="60"/>
-      <c r="U52" s="60"/>
-      <c r="V52" s="60"/>
-      <c r="W52" s="60"/>
-      <c r="X52" s="60"/>
-      <c r="Y52" s="60"/>
-      <c r="Z52" s="60"/>
-      <c r="AA52" s="60"/>
-      <c r="AB52" s="60"/>
-      <c r="AC52" s="60"/>
-      <c r="AD52" s="60"/>
-      <c r="AE52" s="60"/>
-      <c r="AF52" s="60"/>
-      <c r="AG52" s="60"/>
-      <c r="AH52" s="60"/>
-      <c r="AI52" s="60"/>
-      <c r="AJ52" s="136"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="58"/>
+      <c r="K52" s="58"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="58"/>
+      <c r="S52" s="58"/>
+      <c r="T52" s="58"/>
+      <c r="U52" s="58"/>
+      <c r="V52" s="58"/>
+      <c r="W52" s="58"/>
+      <c r="X52" s="58"/>
+      <c r="Y52" s="58"/>
+      <c r="Z52" s="58"/>
+      <c r="AA52" s="58"/>
+      <c r="AB52" s="58"/>
+      <c r="AC52" s="58"/>
+      <c r="AD52" s="58"/>
+      <c r="AE52" s="58"/>
+      <c r="AF52" s="58"/>
+      <c r="AG52" s="58"/>
+      <c r="AH52" s="58"/>
+      <c r="AI52" s="58"/>
+      <c r="AJ52" s="134"/>
       <c r="AK52" s="2"/>
     </row>
     <row r="53" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A53" s="19">
         <v>15</v>
       </c>
-      <c r="B53" s="84"/>
-      <c r="C53" s="85" t="s">
+      <c r="B53" s="82"/>
+      <c r="C53" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="22" t="s">
@@ -4909,8 +4897,8 @@
       <c r="AF53" s="23"/>
       <c r="AG53" s="23"/>
       <c r="AH53" s="23"/>
-      <c r="AI53" s="137"/>
-      <c r="AJ53" s="134"/>
+      <c r="AI53" s="135"/>
+      <c r="AJ53" s="132"/>
       <c r="AK53" s="2"/>
       <c r="AL53" s="3">
         <f>COUNTIF(E57:AI57,22.5)</f>
@@ -4919,8 +4907,8 @@
     </row>
     <row r="54" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A54" s="25"/>
-      <c r="B54" s="75"/>
-      <c r="C54" s="82"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="80"/>
       <c r="D54" s="22" t="s">
         <v>18</v>
       </c>
@@ -4954,51 +4942,51 @@
       <c r="AF54" s="23"/>
       <c r="AG54" s="23"/>
       <c r="AH54" s="23"/>
-      <c r="AI54" s="137"/>
-      <c r="AJ54" s="134"/>
+      <c r="AI54" s="135"/>
+      <c r="AJ54" s="132"/>
       <c r="AK54" s="2"/>
     </row>
     <row r="55" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A55" s="19">
         <v>16</v>
       </c>
-      <c r="B55" s="86"/>
-      <c r="C55" s="85" t="s">
+      <c r="B55" s="84"/>
+      <c r="C55" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D55" s="41"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
-      <c r="H55" s="60"/>
-      <c r="I55" s="60"/>
-      <c r="J55" s="60"/>
-      <c r="K55" s="60"/>
-      <c r="L55" s="60"/>
-      <c r="M55" s="60"/>
-      <c r="N55" s="60"/>
-      <c r="O55" s="60"/>
-      <c r="P55" s="60"/>
-      <c r="Q55" s="60"/>
-      <c r="R55" s="60"/>
-      <c r="S55" s="60"/>
-      <c r="T55" s="60"/>
-      <c r="U55" s="60"/>
-      <c r="V55" s="60"/>
-      <c r="W55" s="60"/>
-      <c r="X55" s="60"/>
-      <c r="Y55" s="60"/>
-      <c r="Z55" s="60"/>
-      <c r="AA55" s="60"/>
-      <c r="AB55" s="60"/>
-      <c r="AC55" s="60"/>
-      <c r="AD55" s="60"/>
-      <c r="AE55" s="60"/>
-      <c r="AF55" s="60"/>
-      <c r="AG55" s="60"/>
-      <c r="AH55" s="60"/>
-      <c r="AI55" s="138"/>
-      <c r="AJ55" s="134"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="58"/>
+      <c r="K55" s="58"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+      <c r="P55" s="58"/>
+      <c r="Q55" s="58"/>
+      <c r="R55" s="58"/>
+      <c r="S55" s="58"/>
+      <c r="T55" s="58"/>
+      <c r="U55" s="58"/>
+      <c r="V55" s="58"/>
+      <c r="W55" s="58"/>
+      <c r="X55" s="58"/>
+      <c r="Y55" s="58"/>
+      <c r="Z55" s="58"/>
+      <c r="AA55" s="58"/>
+      <c r="AB55" s="58"/>
+      <c r="AC55" s="58"/>
+      <c r="AD55" s="58"/>
+      <c r="AE55" s="58"/>
+      <c r="AF55" s="58"/>
+      <c r="AG55" s="58"/>
+      <c r="AH55" s="58"/>
+      <c r="AI55" s="136"/>
+      <c r="AJ55" s="132"/>
       <c r="AK55" s="2"/>
       <c r="AL55" s="3">
         <f>COUNTIF(E59:AI59,22.5)</f>
@@ -5007,8 +4995,8 @@
     </row>
     <row r="56" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A56" s="25"/>
-      <c r="B56" s="84"/>
-      <c r="C56" s="82"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="80"/>
       <c r="D56" s="22" t="s">
         <v>14</v>
       </c>
@@ -5042,16 +5030,16 @@
       <c r="AF56" s="23"/>
       <c r="AG56" s="23"/>
       <c r="AH56" s="23"/>
-      <c r="AI56" s="137"/>
-      <c r="AJ56" s="134"/>
+      <c r="AI56" s="135"/>
+      <c r="AJ56" s="132"/>
       <c r="AK56" s="2"/>
     </row>
     <row r="57" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A57" s="19">
         <v>17</v>
       </c>
-      <c r="B57" s="75"/>
-      <c r="C57" s="85" t="s">
+      <c r="B57" s="73"/>
+      <c r="C57" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="22" t="s">
@@ -5087,8 +5075,8 @@
       <c r="AF57" s="23"/>
       <c r="AG57" s="23"/>
       <c r="AH57" s="23"/>
-      <c r="AI57" s="137"/>
-      <c r="AJ57" s="120"/>
+      <c r="AI57" s="135"/>
+      <c r="AJ57" s="118"/>
       <c r="AK57" s="2"/>
       <c r="AL57" s="3">
         <f>COUNTIF(E61:AI61,22.5)</f>
@@ -5097,88 +5085,88 @@
     </row>
     <row r="58" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A58" s="25"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="41" t="s">
+      <c r="B58" s="85"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="60"/>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="60"/>
-      <c r="O58" s="60"/>
-      <c r="P58" s="60"/>
-      <c r="Q58" s="60"/>
-      <c r="R58" s="60"/>
-      <c r="S58" s="60"/>
-      <c r="T58" s="60"/>
-      <c r="U58" s="60"/>
-      <c r="V58" s="60"/>
-      <c r="W58" s="60"/>
-      <c r="X58" s="60"/>
-      <c r="Y58" s="60"/>
-      <c r="Z58" s="60"/>
-      <c r="AA58" s="60"/>
-      <c r="AB58" s="60"/>
-      <c r="AC58" s="60"/>
-      <c r="AD58" s="60"/>
-      <c r="AE58" s="60"/>
-      <c r="AF58" s="60"/>
-      <c r="AG58" s="60"/>
-      <c r="AH58" s="60"/>
-      <c r="AI58" s="60"/>
-      <c r="AJ58" s="134"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="58"/>
+      <c r="K58" s="58"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+      <c r="P58" s="58"/>
+      <c r="Q58" s="58"/>
+      <c r="R58" s="58"/>
+      <c r="S58" s="58"/>
+      <c r="T58" s="58"/>
+      <c r="U58" s="58"/>
+      <c r="V58" s="58"/>
+      <c r="W58" s="58"/>
+      <c r="X58" s="58"/>
+      <c r="Y58" s="58"/>
+      <c r="Z58" s="58"/>
+      <c r="AA58" s="58"/>
+      <c r="AB58" s="58"/>
+      <c r="AC58" s="58"/>
+      <c r="AD58" s="58"/>
+      <c r="AE58" s="58"/>
+      <c r="AF58" s="58"/>
+      <c r="AG58" s="58"/>
+      <c r="AH58" s="58"/>
+      <c r="AI58" s="58"/>
+      <c r="AJ58" s="132"/>
       <c r="AK58" s="2"/>
     </row>
     <row r="59" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A59" s="19">
         <v>18</v>
       </c>
-      <c r="B59" s="75"/>
-      <c r="C59" s="85" t="s">
+      <c r="B59" s="73"/>
+      <c r="C59" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D59" s="41" t="s">
+      <c r="D59" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="60"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="60"/>
-      <c r="J59" s="60"/>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="60"/>
-      <c r="O59" s="60"/>
-      <c r="P59" s="60"/>
-      <c r="Q59" s="60"/>
-      <c r="R59" s="60"/>
-      <c r="S59" s="60"/>
-      <c r="T59" s="60"/>
-      <c r="U59" s="60"/>
-      <c r="V59" s="60"/>
-      <c r="W59" s="60"/>
-      <c r="X59" s="60"/>
-      <c r="Y59" s="60"/>
-      <c r="Z59" s="60"/>
-      <c r="AA59" s="60"/>
-      <c r="AB59" s="60"/>
-      <c r="AC59" s="60"/>
-      <c r="AD59" s="60"/>
-      <c r="AE59" s="60"/>
-      <c r="AF59" s="60"/>
-      <c r="AG59" s="60"/>
-      <c r="AH59" s="60"/>
-      <c r="AI59" s="60"/>
-      <c r="AJ59" s="120"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
+      <c r="J59" s="58"/>
+      <c r="K59" s="58"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="58"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
+      <c r="S59" s="58"/>
+      <c r="T59" s="58"/>
+      <c r="U59" s="58"/>
+      <c r="V59" s="58"/>
+      <c r="W59" s="58"/>
+      <c r="X59" s="58"/>
+      <c r="Y59" s="58"/>
+      <c r="Z59" s="58"/>
+      <c r="AA59" s="58"/>
+      <c r="AB59" s="58"/>
+      <c r="AC59" s="58"/>
+      <c r="AD59" s="58"/>
+      <c r="AE59" s="58"/>
+      <c r="AF59" s="58"/>
+      <c r="AG59" s="58"/>
+      <c r="AH59" s="58"/>
+      <c r="AI59" s="58"/>
+      <c r="AJ59" s="118"/>
       <c r="AK59" s="2"/>
       <c r="AL59" s="3">
         <f>COUNTIF(E63:AI63,22.5)</f>
@@ -5187,8 +5175,8 @@
     </row>
     <row r="60" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A60" s="25"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="82"/>
+      <c r="B60" s="86"/>
+      <c r="C60" s="80"/>
       <c r="D60" s="22" t="s">
         <v>14</v>
       </c>
@@ -5223,15 +5211,15 @@
       <c r="AG60" s="23"/>
       <c r="AH60" s="23"/>
       <c r="AI60" s="23"/>
-      <c r="AJ60" s="134"/>
+      <c r="AJ60" s="132"/>
       <c r="AK60" s="2"/>
     </row>
     <row r="61" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A61" s="19">
         <v>19</v>
       </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="85" t="s">
+      <c r="B61" s="73"/>
+      <c r="C61" s="83" t="s">
         <v>36</v>
       </c>
       <c r="D61" s="22" t="s">
@@ -5268,7 +5256,7 @@
       <c r="AG61" s="23"/>
       <c r="AH61" s="23"/>
       <c r="AI61" s="23"/>
-      <c r="AJ61" s="120"/>
+      <c r="AJ61" s="118"/>
       <c r="AK61" s="2"/>
       <c r="AL61" s="3">
         <f>COUNTIF(E65:AI65,22.5)</f>
@@ -5277,88 +5265,88 @@
     </row>
     <row r="62" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A62" s="25"/>
-      <c r="B62" s="89"/>
-      <c r="C62" s="82"/>
-      <c r="D62" s="41" t="s">
+      <c r="B62" s="87"/>
+      <c r="C62" s="80"/>
+      <c r="D62" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="60"/>
-      <c r="F62" s="60"/>
-      <c r="G62" s="60"/>
-      <c r="H62" s="60"/>
-      <c r="I62" s="60"/>
-      <c r="J62" s="60"/>
-      <c r="K62" s="60"/>
-      <c r="L62" s="60"/>
-      <c r="M62" s="60"/>
-      <c r="N62" s="60"/>
-      <c r="O62" s="60"/>
-      <c r="P62" s="60"/>
-      <c r="Q62" s="60"/>
-      <c r="R62" s="60"/>
-      <c r="S62" s="60"/>
-      <c r="T62" s="60"/>
-      <c r="U62" s="60"/>
-      <c r="V62" s="60"/>
-      <c r="W62" s="60"/>
-      <c r="X62" s="60"/>
-      <c r="Y62" s="60"/>
-      <c r="Z62" s="60"/>
-      <c r="AA62" s="60"/>
-      <c r="AB62" s="60"/>
-      <c r="AC62" s="60"/>
-      <c r="AD62" s="60"/>
-      <c r="AE62" s="60"/>
-      <c r="AF62" s="60"/>
-      <c r="AG62" s="60"/>
-      <c r="AH62" s="60"/>
-      <c r="AI62" s="60"/>
-      <c r="AJ62" s="134"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="58"/>
+      <c r="L62" s="58"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="58"/>
+      <c r="V62" s="58"/>
+      <c r="W62" s="58"/>
+      <c r="X62" s="58"/>
+      <c r="Y62" s="58"/>
+      <c r="Z62" s="58"/>
+      <c r="AA62" s="58"/>
+      <c r="AB62" s="58"/>
+      <c r="AC62" s="58"/>
+      <c r="AD62" s="58"/>
+      <c r="AE62" s="58"/>
+      <c r="AF62" s="58"/>
+      <c r="AG62" s="58"/>
+      <c r="AH62" s="58"/>
+      <c r="AI62" s="58"/>
+      <c r="AJ62" s="132"/>
       <c r="AK62" s="2"/>
     </row>
     <row r="63" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A63" s="19">
         <v>20</v>
       </c>
-      <c r="B63" s="75"/>
-      <c r="C63" s="85" t="s">
+      <c r="B63" s="73"/>
+      <c r="C63" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="41" t="s">
+      <c r="D63" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E63" s="60"/>
-      <c r="F63" s="60"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="60"/>
-      <c r="I63" s="60"/>
-      <c r="J63" s="60"/>
-      <c r="K63" s="60"/>
-      <c r="L63" s="60"/>
-      <c r="M63" s="60"/>
-      <c r="N63" s="60"/>
-      <c r="O63" s="60"/>
-      <c r="P63" s="60"/>
-      <c r="Q63" s="60"/>
-      <c r="R63" s="60"/>
-      <c r="S63" s="60"/>
-      <c r="T63" s="60"/>
-      <c r="U63" s="60"/>
-      <c r="V63" s="60"/>
-      <c r="W63" s="60"/>
-      <c r="X63" s="60"/>
-      <c r="Y63" s="60"/>
-      <c r="Z63" s="60"/>
-      <c r="AA63" s="60"/>
-      <c r="AB63" s="60"/>
-      <c r="AC63" s="60"/>
-      <c r="AD63" s="60"/>
-      <c r="AE63" s="60"/>
-      <c r="AF63" s="60"/>
-      <c r="AG63" s="60"/>
-      <c r="AH63" s="60"/>
-      <c r="AI63" s="60"/>
-      <c r="AJ63" s="120"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="58"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="58"/>
+      <c r="Q63" s="58"/>
+      <c r="R63" s="58"/>
+      <c r="S63" s="58"/>
+      <c r="T63" s="58"/>
+      <c r="U63" s="58"/>
+      <c r="V63" s="58"/>
+      <c r="W63" s="58"/>
+      <c r="X63" s="58"/>
+      <c r="Y63" s="58"/>
+      <c r="Z63" s="58"/>
+      <c r="AA63" s="58"/>
+      <c r="AB63" s="58"/>
+      <c r="AC63" s="58"/>
+      <c r="AD63" s="58"/>
+      <c r="AE63" s="58"/>
+      <c r="AF63" s="58"/>
+      <c r="AG63" s="58"/>
+      <c r="AH63" s="58"/>
+      <c r="AI63" s="58"/>
+      <c r="AJ63" s="118"/>
       <c r="AK63" s="2"/>
       <c r="AL63" s="3">
         <f>COUNTIF(E67:AI67,22.5)</f>
@@ -5367,8 +5355,8 @@
     </row>
     <row r="64" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A64" s="25"/>
-      <c r="B64" s="88"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="86"/>
+      <c r="C64" s="80"/>
       <c r="D64" s="22" t="s">
         <v>14</v>
       </c>
@@ -5403,15 +5391,15 @@
       <c r="AG64" s="23"/>
       <c r="AH64" s="23"/>
       <c r="AI64" s="23"/>
-      <c r="AJ64" s="134"/>
+      <c r="AJ64" s="132"/>
       <c r="AK64" s="2"/>
     </row>
     <row r="65" ht="12" hidden="1" customHeight="1" spans="1:38">
       <c r="A65" s="19">
         <v>21</v>
       </c>
-      <c r="B65" s="75"/>
-      <c r="C65" s="141" t="s">
+      <c r="B65" s="73"/>
+      <c r="C65" s="139" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="22" t="s">
@@ -5448,7 +5436,7 @@
       <c r="AG65" s="23"/>
       <c r="AH65" s="23"/>
       <c r="AI65" s="23"/>
-      <c r="AJ65" s="120"/>
+      <c r="AJ65" s="118"/>
       <c r="AK65" s="2"/>
       <c r="AL65" s="3">
         <f>COUNTIF(E69:AI69,22.5)</f>
@@ -5457,92 +5445,92 @@
     </row>
     <row r="66" ht="12" hidden="1" customHeight="1" spans="1:37">
       <c r="A66" s="25"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="82"/>
-      <c r="D66" s="41" t="s">
+      <c r="B66" s="87"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="60"/>
-      <c r="F66" s="60"/>
-      <c r="G66" s="60"/>
-      <c r="H66" s="60"/>
-      <c r="I66" s="60"/>
-      <c r="J66" s="60"/>
-      <c r="K66" s="60"/>
-      <c r="L66" s="60"/>
-      <c r="M66" s="60"/>
-      <c r="N66" s="60"/>
-      <c r="O66" s="60"/>
-      <c r="P66" s="60"/>
-      <c r="Q66" s="60"/>
-      <c r="R66" s="60"/>
-      <c r="S66" s="60"/>
-      <c r="T66" s="60"/>
-      <c r="U66" s="60"/>
-      <c r="V66" s="60"/>
-      <c r="W66" s="60"/>
-      <c r="X66" s="60"/>
-      <c r="Y66" s="60"/>
-      <c r="Z66" s="60"/>
-      <c r="AA66" s="60"/>
-      <c r="AB66" s="60"/>
-      <c r="AC66" s="60"/>
-      <c r="AD66" s="60"/>
-      <c r="AE66" s="60"/>
-      <c r="AF66" s="60"/>
-      <c r="AG66" s="60"/>
-      <c r="AH66" s="60"/>
-      <c r="AI66" s="138"/>
-      <c r="AJ66" s="134"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="58"/>
+      <c r="J66" s="58"/>
+      <c r="K66" s="58"/>
+      <c r="L66" s="58"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="58"/>
+      <c r="O66" s="58"/>
+      <c r="P66" s="58"/>
+      <c r="Q66" s="58"/>
+      <c r="R66" s="58"/>
+      <c r="S66" s="58"/>
+      <c r="T66" s="58"/>
+      <c r="U66" s="58"/>
+      <c r="V66" s="58"/>
+      <c r="W66" s="58"/>
+      <c r="X66" s="58"/>
+      <c r="Y66" s="58"/>
+      <c r="Z66" s="58"/>
+      <c r="AA66" s="58"/>
+      <c r="AB66" s="58"/>
+      <c r="AC66" s="58"/>
+      <c r="AD66" s="58"/>
+      <c r="AE66" s="58"/>
+      <c r="AF66" s="58"/>
+      <c r="AG66" s="58"/>
+      <c r="AH66" s="58"/>
+      <c r="AI66" s="136"/>
+      <c r="AJ66" s="132"/>
       <c r="AK66" s="2"/>
     </row>
     <row r="67" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A67" s="19">
         <v>22</v>
       </c>
-      <c r="B67" s="75"/>
-      <c r="C67" s="142"/>
-      <c r="D67" s="41" t="s">
+      <c r="B67" s="73"/>
+      <c r="C67" s="140"/>
+      <c r="D67" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="60"/>
-      <c r="J67" s="60"/>
-      <c r="K67" s="60"/>
-      <c r="L67" s="60"/>
-      <c r="M67" s="60"/>
-      <c r="N67" s="60"/>
-      <c r="O67" s="60"/>
-      <c r="P67" s="60"/>
-      <c r="Q67" s="60"/>
-      <c r="R67" s="60"/>
-      <c r="S67" s="60"/>
-      <c r="T67" s="60"/>
-      <c r="U67" s="60"/>
-      <c r="V67" s="60"/>
-      <c r="W67" s="60"/>
-      <c r="X67" s="60"/>
-      <c r="Y67" s="60"/>
-      <c r="Z67" s="60"/>
-      <c r="AA67" s="60"/>
-      <c r="AB67" s="60"/>
-      <c r="AC67" s="60"/>
-      <c r="AD67" s="60"/>
-      <c r="AE67" s="60"/>
-      <c r="AF67" s="60"/>
-      <c r="AG67" s="60"/>
-      <c r="AH67" s="60"/>
-      <c r="AI67" s="138"/>
-      <c r="AJ67" s="120"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
+      <c r="J67" s="58"/>
+      <c r="K67" s="58"/>
+      <c r="L67" s="58"/>
+      <c r="M67" s="58"/>
+      <c r="N67" s="58"/>
+      <c r="O67" s="58"/>
+      <c r="P67" s="58"/>
+      <c r="Q67" s="58"/>
+      <c r="R67" s="58"/>
+      <c r="S67" s="58"/>
+      <c r="T67" s="58"/>
+      <c r="U67" s="58"/>
+      <c r="V67" s="58"/>
+      <c r="W67" s="58"/>
+      <c r="X67" s="58"/>
+      <c r="Y67" s="58"/>
+      <c r="Z67" s="58"/>
+      <c r="AA67" s="58"/>
+      <c r="AB67" s="58"/>
+      <c r="AC67" s="58"/>
+      <c r="AD67" s="58"/>
+      <c r="AE67" s="58"/>
+      <c r="AF67" s="58"/>
+      <c r="AG67" s="58"/>
+      <c r="AH67" s="58"/>
+      <c r="AI67" s="136"/>
+      <c r="AJ67" s="118"/>
       <c r="AK67" s="2"/>
     </row>
     <row r="68" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A68" s="25"/>
-      <c r="B68" s="88"/>
-      <c r="C68" s="143"/>
+      <c r="B68" s="86"/>
+      <c r="C68" s="141"/>
       <c r="D68" s="22" t="s">
         <v>14</v>
       </c>
@@ -5577,15 +5565,15 @@
       <c r="AG68" s="23"/>
       <c r="AH68" s="23"/>
       <c r="AI68" s="23"/>
-      <c r="AJ68" s="134"/>
+      <c r="AJ68" s="132"/>
       <c r="AK68" s="2"/>
     </row>
     <row r="69" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A69" s="19">
         <v>23</v>
       </c>
-      <c r="B69" s="75"/>
-      <c r="C69" s="144"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="142"/>
       <c r="D69" s="22" t="s">
         <v>18</v>
       </c>
@@ -5620,98 +5608,98 @@
       <c r="AG69" s="23"/>
       <c r="AH69" s="23"/>
       <c r="AI69" s="23"/>
-      <c r="AJ69" s="120"/>
+      <c r="AJ69" s="118"/>
       <c r="AK69" s="2"/>
     </row>
     <row r="70" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A70" s="25"/>
-      <c r="B70" s="89"/>
-      <c r="C70" s="145"/>
-      <c r="D70" s="41" t="s">
+      <c r="B70" s="87"/>
+      <c r="C70" s="143"/>
+      <c r="D70" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="60"/>
-      <c r="F70" s="60"/>
-      <c r="G70" s="60"/>
-      <c r="H70" s="60"/>
-      <c r="I70" s="60"/>
-      <c r="J70" s="60"/>
-      <c r="K70" s="60"/>
-      <c r="L70" s="60"/>
-      <c r="M70" s="60"/>
-      <c r="N70" s="60"/>
-      <c r="O70" s="60"/>
-      <c r="P70" s="60"/>
-      <c r="Q70" s="60"/>
-      <c r="R70" s="60"/>
-      <c r="S70" s="60"/>
-      <c r="T70" s="60"/>
-      <c r="U70" s="60"/>
-      <c r="V70" s="60"/>
-      <c r="W70" s="60"/>
-      <c r="X70" s="60"/>
-      <c r="Y70" s="60"/>
-      <c r="Z70" s="60"/>
-      <c r="AA70" s="60"/>
-      <c r="AB70" s="60"/>
-      <c r="AC70" s="60"/>
-      <c r="AD70" s="60"/>
-      <c r="AE70" s="60"/>
-      <c r="AF70" s="60"/>
-      <c r="AG70" s="60"/>
-      <c r="AH70" s="60"/>
-      <c r="AI70" s="60"/>
-      <c r="AJ70" s="134"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="58"/>
+      <c r="K70" s="58"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="58"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="58"/>
+      <c r="P70" s="58"/>
+      <c r="Q70" s="58"/>
+      <c r="R70" s="58"/>
+      <c r="S70" s="58"/>
+      <c r="T70" s="58"/>
+      <c r="U70" s="58"/>
+      <c r="V70" s="58"/>
+      <c r="W70" s="58"/>
+      <c r="X70" s="58"/>
+      <c r="Y70" s="58"/>
+      <c r="Z70" s="58"/>
+      <c r="AA70" s="58"/>
+      <c r="AB70" s="58"/>
+      <c r="AC70" s="58"/>
+      <c r="AD70" s="58"/>
+      <c r="AE70" s="58"/>
+      <c r="AF70" s="58"/>
+      <c r="AG70" s="58"/>
+      <c r="AH70" s="58"/>
+      <c r="AI70" s="58"/>
+      <c r="AJ70" s="132"/>
       <c r="AK70" s="2"/>
     </row>
     <row r="71" ht="20.25" hidden="1" customHeight="1" spans="1:38">
       <c r="A71" s="19">
         <v>24</v>
       </c>
-      <c r="B71" s="75"/>
-      <c r="C71" s="142"/>
-      <c r="D71" s="41" t="s">
+      <c r="B71" s="73"/>
+      <c r="C71" s="140"/>
+      <c r="D71" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="60"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="60"/>
-      <c r="O71" s="60"/>
-      <c r="P71" s="60"/>
-      <c r="Q71" s="60"/>
-      <c r="R71" s="60"/>
-      <c r="S71" s="60"/>
-      <c r="T71" s="60"/>
-      <c r="U71" s="60"/>
-      <c r="V71" s="60"/>
-      <c r="W71" s="60"/>
-      <c r="X71" s="60"/>
-      <c r="Y71" s="60"/>
-      <c r="Z71" s="60"/>
-      <c r="AA71" s="60"/>
-      <c r="AB71" s="60"/>
-      <c r="AC71" s="60"/>
-      <c r="AD71" s="60"/>
-      <c r="AE71" s="60"/>
-      <c r="AF71" s="60"/>
-      <c r="AG71" s="60"/>
-      <c r="AH71" s="60"/>
-      <c r="AI71" s="60"/>
-      <c r="AJ71" s="120"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="58"/>
+      <c r="H71" s="58"/>
+      <c r="I71" s="58"/>
+      <c r="J71" s="58"/>
+      <c r="K71" s="58"/>
+      <c r="L71" s="58"/>
+      <c r="M71" s="58"/>
+      <c r="N71" s="58"/>
+      <c r="O71" s="58"/>
+      <c r="P71" s="58"/>
+      <c r="Q71" s="58"/>
+      <c r="R71" s="58"/>
+      <c r="S71" s="58"/>
+      <c r="T71" s="58"/>
+      <c r="U71" s="58"/>
+      <c r="V71" s="58"/>
+      <c r="W71" s="58"/>
+      <c r="X71" s="58"/>
+      <c r="Y71" s="58"/>
+      <c r="Z71" s="58"/>
+      <c r="AA71" s="58"/>
+      <c r="AB71" s="58"/>
+      <c r="AC71" s="58"/>
+      <c r="AD71" s="58"/>
+      <c r="AE71" s="58"/>
+      <c r="AF71" s="58"/>
+      <c r="AG71" s="58"/>
+      <c r="AH71" s="58"/>
+      <c r="AI71" s="58"/>
+      <c r="AJ71" s="118"/>
       <c r="AK71" s="2"/>
       <c r="AL71" s="1"/>
     </row>
     <row r="72" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A72" s="25"/>
-      <c r="B72" s="146"/>
-      <c r="C72" s="147"/>
+      <c r="B72" s="144"/>
+      <c r="C72" s="145"/>
       <c r="D72" s="22" t="s">
         <v>14</v>
       </c>
@@ -5746,15 +5734,15 @@
       <c r="AG72" s="23"/>
       <c r="AH72" s="23"/>
       <c r="AI72" s="23"/>
-      <c r="AJ72" s="134"/>
+      <c r="AJ72" s="132"/>
       <c r="AK72" s="2"/>
     </row>
     <row r="73" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A73" s="19">
         <v>25</v>
       </c>
-      <c r="B73" s="75"/>
-      <c r="C73" s="144"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="142"/>
       <c r="D73" s="22" t="s">
         <v>18</v>
       </c>
@@ -5789,98 +5777,98 @@
       <c r="AG73" s="23"/>
       <c r="AH73" s="23"/>
       <c r="AI73" s="23"/>
-      <c r="AJ73" s="120"/>
+      <c r="AJ73" s="118"/>
       <c r="AK73" s="2"/>
     </row>
     <row r="74" ht="20.25" hidden="1" customHeight="1" spans="1:37">
       <c r="A74" s="25"/>
-      <c r="B74" s="89"/>
-      <c r="C74" s="145"/>
-      <c r="D74" s="41" t="s">
+      <c r="B74" s="87"/>
+      <c r="C74" s="143"/>
+      <c r="D74" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="60"/>
-      <c r="F74" s="60"/>
-      <c r="G74" s="60"/>
-      <c r="H74" s="60"/>
-      <c r="I74" s="60"/>
-      <c r="J74" s="60"/>
-      <c r="K74" s="60"/>
-      <c r="L74" s="60"/>
-      <c r="M74" s="60"/>
-      <c r="N74" s="60"/>
-      <c r="O74" s="60"/>
-      <c r="P74" s="60"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="60"/>
-      <c r="S74" s="60"/>
-      <c r="T74" s="60"/>
-      <c r="U74" s="60"/>
-      <c r="V74" s="60"/>
-      <c r="W74" s="60"/>
-      <c r="X74" s="60"/>
-      <c r="Y74" s="60"/>
-      <c r="Z74" s="60"/>
-      <c r="AA74" s="60"/>
-      <c r="AB74" s="60"/>
-      <c r="AC74" s="60"/>
-      <c r="AD74" s="60"/>
-      <c r="AE74" s="60"/>
-      <c r="AF74" s="60"/>
-      <c r="AG74" s="60"/>
-      <c r="AH74" s="60"/>
-      <c r="AI74" s="60"/>
-      <c r="AJ74" s="134"/>
+      <c r="E74" s="58"/>
+      <c r="F74" s="58"/>
+      <c r="G74" s="58"/>
+      <c r="H74" s="58"/>
+      <c r="I74" s="58"/>
+      <c r="J74" s="58"/>
+      <c r="K74" s="58"/>
+      <c r="L74" s="58"/>
+      <c r="M74" s="58"/>
+      <c r="N74" s="58"/>
+      <c r="O74" s="58"/>
+      <c r="P74" s="58"/>
+      <c r="Q74" s="58"/>
+      <c r="R74" s="58"/>
+      <c r="S74" s="58"/>
+      <c r="T74" s="58"/>
+      <c r="U74" s="58"/>
+      <c r="V74" s="58"/>
+      <c r="W74" s="58"/>
+      <c r="X74" s="58"/>
+      <c r="Y74" s="58"/>
+      <c r="Z74" s="58"/>
+      <c r="AA74" s="58"/>
+      <c r="AB74" s="58"/>
+      <c r="AC74" s="58"/>
+      <c r="AD74" s="58"/>
+      <c r="AE74" s="58"/>
+      <c r="AF74" s="58"/>
+      <c r="AG74" s="58"/>
+      <c r="AH74" s="58"/>
+      <c r="AI74" s="58"/>
+      <c r="AJ74" s="132"/>
       <c r="AK74" s="2"/>
     </row>
     <row r="75" ht="20.25" hidden="1" customHeight="1" spans="1:38">
       <c r="A75" s="19">
         <v>26</v>
       </c>
-      <c r="B75" s="75"/>
-      <c r="C75" s="142"/>
-      <c r="D75" s="41" t="s">
+      <c r="B75" s="73"/>
+      <c r="C75" s="140"/>
+      <c r="D75" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E75" s="60"/>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="60"/>
-      <c r="K75" s="60"/>
-      <c r="L75" s="60"/>
-      <c r="M75" s="60"/>
-      <c r="N75" s="60"/>
-      <c r="O75" s="60"/>
-      <c r="P75" s="60"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="60"/>
-      <c r="S75" s="60"/>
-      <c r="T75" s="60"/>
-      <c r="U75" s="60"/>
-      <c r="V75" s="60"/>
-      <c r="W75" s="60"/>
-      <c r="X75" s="60"/>
-      <c r="Y75" s="60"/>
-      <c r="Z75" s="60"/>
-      <c r="AA75" s="60"/>
-      <c r="AB75" s="60"/>
-      <c r="AC75" s="60"/>
-      <c r="AD75" s="60"/>
-      <c r="AE75" s="60"/>
-      <c r="AF75" s="60"/>
-      <c r="AG75" s="60"/>
-      <c r="AH75" s="60"/>
-      <c r="AI75" s="60"/>
-      <c r="AJ75" s="120"/>
+      <c r="E75" s="58"/>
+      <c r="F75" s="58"/>
+      <c r="G75" s="58"/>
+      <c r="H75" s="58"/>
+      <c r="I75" s="58"/>
+      <c r="J75" s="58"/>
+      <c r="K75" s="58"/>
+      <c r="L75" s="58"/>
+      <c r="M75" s="58"/>
+      <c r="N75" s="58"/>
+      <c r="O75" s="58"/>
+      <c r="P75" s="58"/>
+      <c r="Q75" s="58"/>
+      <c r="R75" s="58"/>
+      <c r="S75" s="58"/>
+      <c r="T75" s="58"/>
+      <c r="U75" s="58"/>
+      <c r="V75" s="58"/>
+      <c r="W75" s="58"/>
+      <c r="X75" s="58"/>
+      <c r="Y75" s="58"/>
+      <c r="Z75" s="58"/>
+      <c r="AA75" s="58"/>
+      <c r="AB75" s="58"/>
+      <c r="AC75" s="58"/>
+      <c r="AD75" s="58"/>
+      <c r="AE75" s="58"/>
+      <c r="AF75" s="58"/>
+      <c r="AG75" s="58"/>
+      <c r="AH75" s="58"/>
+      <c r="AI75" s="58"/>
+      <c r="AJ75" s="118"/>
       <c r="AK75" s="2"/>
       <c r="AL75" s="1"/>
     </row>
     <row r="76" ht="20.25" hidden="1" customHeight="1" spans="1:39">
       <c r="A76" s="25"/>
-      <c r="B76" s="146"/>
-      <c r="C76" s="147"/>
+      <c r="B76" s="144"/>
+      <c r="C76" s="145"/>
       <c r="D76" s="22" t="s">
         <v>14</v>
       </c>
@@ -5915,7 +5903,7 @@
       <c r="AG76" s="23"/>
       <c r="AH76" s="23"/>
       <c r="AI76" s="23"/>
-      <c r="AJ76" s="134"/>
+      <c r="AJ76" s="132"/>
       <c r="AK76" s="2"/>
       <c r="AL76" s="1"/>
       <c r="AM76" s="1"/>
@@ -5924,8 +5912,8 @@
       <c r="A77" s="19">
         <v>27</v>
       </c>
-      <c r="B77" s="75"/>
-      <c r="C77" s="144"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="142"/>
       <c r="D77" s="22" t="s">
         <v>18</v>
       </c>
@@ -5960,243 +5948,243 @@
       <c r="AG77" s="23"/>
       <c r="AH77" s="23"/>
       <c r="AI77" s="23"/>
-      <c r="AJ77" s="120"/>
+      <c r="AJ77" s="118"/>
       <c r="AK77" s="2"/>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
     </row>
     <row r="78" ht="30.95" customHeight="1" spans="1:39">
       <c r="A78" s="25"/>
-      <c r="B78" s="148"/>
-      <c r="D78" s="149"/>
-      <c r="E78" s="150"/>
-      <c r="F78" s="150"/>
-      <c r="G78" s="150"/>
-      <c r="H78" s="150"/>
-      <c r="I78" s="150"/>
-      <c r="J78" s="150"/>
-      <c r="K78" s="150"/>
-      <c r="L78" s="150"/>
-      <c r="M78" s="150"/>
-      <c r="N78" s="150"/>
-      <c r="O78" s="150"/>
-      <c r="P78" s="150"/>
-      <c r="Q78" s="150"/>
-      <c r="R78" s="150"/>
-      <c r="S78" s="150"/>
-      <c r="T78" s="150"/>
-      <c r="U78" s="150"/>
-      <c r="V78" s="150"/>
-      <c r="W78" s="150"/>
-      <c r="X78" s="150"/>
-      <c r="Y78" s="150"/>
-      <c r="Z78" s="150"/>
-      <c r="AA78" s="150"/>
-      <c r="AB78" s="150"/>
-      <c r="AC78" s="150"/>
-      <c r="AD78" s="150"/>
-      <c r="AE78" s="150"/>
-      <c r="AF78" s="150"/>
-      <c r="AG78" s="150"/>
-      <c r="AH78" s="150"/>
-      <c r="AI78" s="150"/>
-      <c r="AJ78" s="169"/>
+      <c r="B78" s="146"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="148"/>
+      <c r="F78" s="148"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="148"/>
+      <c r="I78" s="148"/>
+      <c r="J78" s="148"/>
+      <c r="K78" s="148"/>
+      <c r="L78" s="148"/>
+      <c r="M78" s="148"/>
+      <c r="N78" s="148"/>
+      <c r="O78" s="148"/>
+      <c r="P78" s="148"/>
+      <c r="Q78" s="148"/>
+      <c r="R78" s="148"/>
+      <c r="S78" s="148"/>
+      <c r="T78" s="148"/>
+      <c r="U78" s="148"/>
+      <c r="V78" s="148"/>
+      <c r="W78" s="148"/>
+      <c r="X78" s="148"/>
+      <c r="Y78" s="148"/>
+      <c r="Z78" s="148"/>
+      <c r="AA78" s="148"/>
+      <c r="AB78" s="148"/>
+      <c r="AC78" s="148"/>
+      <c r="AD78" s="148"/>
+      <c r="AE78" s="148"/>
+      <c r="AF78" s="148"/>
+      <c r="AG78" s="148"/>
+      <c r="AH78" s="148"/>
+      <c r="AI78" s="148"/>
+      <c r="AJ78" s="167"/>
       <c r="AK78" s="2"/>
-      <c r="AM78" s="170"/>
+      <c r="AM78" s="168"/>
     </row>
     <row r="79" ht="12" customHeight="1" spans="1:37">
-      <c r="A79" s="151"/>
-      <c r="B79" s="152"/>
-      <c r="C79" s="152"/>
-      <c r="D79" s="152"/>
-      <c r="E79" s="153"/>
-      <c r="F79" s="153"/>
-      <c r="G79" s="153"/>
-      <c r="H79" s="153"/>
-      <c r="I79" s="153"/>
-      <c r="J79" s="153"/>
-      <c r="K79" s="153"/>
-      <c r="L79" s="153"/>
-      <c r="M79" s="153"/>
-      <c r="N79" s="153"/>
-      <c r="O79" s="153"/>
-      <c r="P79" s="153"/>
-      <c r="Q79" s="153"/>
-      <c r="R79" s="153"/>
-      <c r="S79" s="153"/>
-      <c r="T79" s="153"/>
-      <c r="U79" s="153"/>
-      <c r="V79" s="153"/>
-      <c r="W79" s="153"/>
-      <c r="X79" s="153"/>
-      <c r="Y79" s="153"/>
-      <c r="Z79" s="153"/>
-      <c r="AA79" s="153"/>
-      <c r="AB79" s="153"/>
-      <c r="AC79" s="153"/>
-      <c r="AD79" s="153"/>
-      <c r="AE79" s="153"/>
-      <c r="AF79" s="153"/>
-      <c r="AG79" s="153"/>
-      <c r="AH79" s="153"/>
-      <c r="AI79" s="153"/>
-      <c r="AJ79" s="171"/>
+      <c r="A79" s="149"/>
+      <c r="B79" s="150"/>
+      <c r="C79" s="150"/>
+      <c r="D79" s="150"/>
+      <c r="E79" s="151"/>
+      <c r="F79" s="151"/>
+      <c r="G79" s="151"/>
+      <c r="H79" s="151"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="151"/>
+      <c r="K79" s="151"/>
+      <c r="L79" s="151"/>
+      <c r="M79" s="151"/>
+      <c r="N79" s="151"/>
+      <c r="O79" s="151"/>
+      <c r="P79" s="151"/>
+      <c r="Q79" s="151"/>
+      <c r="R79" s="151"/>
+      <c r="S79" s="151"/>
+      <c r="T79" s="151"/>
+      <c r="U79" s="151"/>
+      <c r="V79" s="151"/>
+      <c r="W79" s="151"/>
+      <c r="X79" s="151"/>
+      <c r="Y79" s="151"/>
+      <c r="Z79" s="151"/>
+      <c r="AA79" s="151"/>
+      <c r="AB79" s="151"/>
+      <c r="AC79" s="151"/>
+      <c r="AD79" s="151"/>
+      <c r="AE79" s="151"/>
+      <c r="AF79" s="151"/>
+      <c r="AG79" s="151"/>
+      <c r="AH79" s="151"/>
+      <c r="AI79" s="151"/>
+      <c r="AJ79" s="169"/>
       <c r="AK79" s="2"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:37">
       <c r="A80" s="25"/>
       <c r="B80" s="27"/>
-      <c r="C80" s="154"/>
-      <c r="D80" s="154"/>
-      <c r="E80" s="155"/>
-      <c r="F80" s="156"/>
-      <c r="G80" s="157"/>
-      <c r="H80" s="157"/>
-      <c r="I80" s="157"/>
-      <c r="J80" s="157"/>
-      <c r="K80" s="157"/>
-      <c r="L80" s="157"/>
-      <c r="M80" s="157"/>
-      <c r="N80" s="157"/>
-      <c r="O80" s="157"/>
-      <c r="P80" s="157"/>
-      <c r="Q80" s="157"/>
-      <c r="R80" s="157"/>
-      <c r="S80" s="157"/>
-      <c r="T80" s="157"/>
-      <c r="U80" s="157"/>
-      <c r="V80" s="154"/>
-      <c r="W80" s="154"/>
-      <c r="X80" s="154"/>
-      <c r="Y80" s="154"/>
-      <c r="Z80" s="154"/>
-      <c r="AA80" s="154"/>
-      <c r="AB80" s="168"/>
-      <c r="AC80" s="154"/>
-      <c r="AD80" s="154"/>
-      <c r="AE80" s="154"/>
-      <c r="AF80" s="154"/>
-      <c r="AG80" s="172"/>
-      <c r="AH80" s="154"/>
-      <c r="AI80" s="154"/>
-      <c r="AJ80" s="120"/>
+      <c r="C80" s="152"/>
+      <c r="D80" s="152"/>
+      <c r="E80" s="153"/>
+      <c r="F80" s="154"/>
+      <c r="G80" s="155"/>
+      <c r="H80" s="155"/>
+      <c r="I80" s="155"/>
+      <c r="J80" s="155"/>
+      <c r="K80" s="155"/>
+      <c r="L80" s="155"/>
+      <c r="M80" s="155"/>
+      <c r="N80" s="155"/>
+      <c r="O80" s="155"/>
+      <c r="P80" s="155"/>
+      <c r="Q80" s="155"/>
+      <c r="R80" s="155"/>
+      <c r="S80" s="155"/>
+      <c r="T80" s="155"/>
+      <c r="U80" s="155"/>
+      <c r="V80" s="152"/>
+      <c r="W80" s="152"/>
+      <c r="X80" s="152"/>
+      <c r="Y80" s="152"/>
+      <c r="Z80" s="152"/>
+      <c r="AA80" s="152"/>
+      <c r="AB80" s="166"/>
+      <c r="AC80" s="152"/>
+      <c r="AD80" s="152"/>
+      <c r="AE80" s="152"/>
+      <c r="AF80" s="152"/>
+      <c r="AG80" s="170"/>
+      <c r="AH80" s="152"/>
+      <c r="AI80" s="152"/>
+      <c r="AJ80" s="118"/>
       <c r="AK80" s="2"/>
     </row>
     <row r="81" spans="1:37">
       <c r="A81" s="28"/>
-      <c r="B81" s="154"/>
-      <c r="C81" s="158"/>
-      <c r="D81" s="159"/>
-      <c r="E81" s="154"/>
-      <c r="F81" s="154"/>
-      <c r="G81" s="154"/>
-      <c r="H81" s="154"/>
-      <c r="I81" s="154"/>
-      <c r="J81" s="154"/>
-      <c r="K81" s="154"/>
-      <c r="L81" s="154"/>
-      <c r="M81" s="154"/>
-      <c r="N81" s="154"/>
-      <c r="O81" s="154"/>
-      <c r="P81" s="154"/>
-      <c r="Q81" s="154"/>
-      <c r="R81" s="154"/>
-      <c r="S81" s="154"/>
-      <c r="T81" s="154"/>
-      <c r="U81" s="154"/>
-      <c r="V81" s="154"/>
-      <c r="W81" s="154"/>
-      <c r="X81" s="154"/>
-      <c r="Y81" s="154"/>
-      <c r="Z81" s="154"/>
-      <c r="AA81" s="154"/>
-      <c r="AB81" s="154"/>
-      <c r="AC81" s="154"/>
-      <c r="AD81" s="154"/>
-      <c r="AE81" s="154"/>
-      <c r="AF81" s="154"/>
-      <c r="AG81" s="154"/>
-      <c r="AH81" s="154"/>
-      <c r="AI81" s="173"/>
-      <c r="AJ81" s="174"/>
+      <c r="B81" s="152"/>
+      <c r="C81" s="156"/>
+      <c r="D81" s="157"/>
+      <c r="E81" s="152"/>
+      <c r="F81" s="152"/>
+      <c r="G81" s="152"/>
+      <c r="H81" s="152"/>
+      <c r="I81" s="152"/>
+      <c r="J81" s="152"/>
+      <c r="K81" s="152"/>
+      <c r="L81" s="152"/>
+      <c r="M81" s="152"/>
+      <c r="N81" s="152"/>
+      <c r="O81" s="152"/>
+      <c r="P81" s="152"/>
+      <c r="Q81" s="152"/>
+      <c r="R81" s="152"/>
+      <c r="S81" s="152"/>
+      <c r="T81" s="152"/>
+      <c r="U81" s="152"/>
+      <c r="V81" s="152"/>
+      <c r="W81" s="152"/>
+      <c r="X81" s="152"/>
+      <c r="Y81" s="152"/>
+      <c r="Z81" s="152"/>
+      <c r="AA81" s="152"/>
+      <c r="AB81" s="152"/>
+      <c r="AC81" s="152"/>
+      <c r="AD81" s="152"/>
+      <c r="AE81" s="152"/>
+      <c r="AF81" s="152"/>
+      <c r="AG81" s="152"/>
+      <c r="AH81" s="152"/>
+      <c r="AI81" s="171"/>
+      <c r="AJ81" s="172"/>
       <c r="AK81" s="2"/>
     </row>
     <row r="82" spans="1:37">
       <c r="A82" s="25"/>
-      <c r="B82" s="160"/>
-      <c r="C82" s="158"/>
-      <c r="D82" s="159"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="154"/>
-      <c r="G82" s="154"/>
-      <c r="H82" s="154"/>
-      <c r="I82" s="154"/>
-      <c r="J82" s="154"/>
-      <c r="K82" s="154"/>
-      <c r="L82" s="154"/>
-      <c r="M82" s="154"/>
-      <c r="N82" s="154"/>
-      <c r="O82" s="154"/>
-      <c r="P82" s="154"/>
-      <c r="Q82" s="154"/>
-      <c r="R82" s="154"/>
-      <c r="S82" s="154"/>
-      <c r="T82" s="165"/>
-      <c r="U82" s="166"/>
-      <c r="V82" s="166"/>
-      <c r="W82" s="166"/>
-      <c r="X82" s="166"/>
-      <c r="Y82" s="166"/>
-      <c r="Z82" s="166"/>
-      <c r="AA82" s="166"/>
-      <c r="AB82" s="166"/>
-      <c r="AC82" s="166"/>
-      <c r="AD82" s="166"/>
-      <c r="AE82" s="166"/>
-      <c r="AF82" s="166"/>
-      <c r="AG82" s="166"/>
-      <c r="AH82" s="166"/>
-      <c r="AI82" s="175"/>
-      <c r="AJ82" s="120"/>
+      <c r="B82" s="158"/>
+      <c r="C82" s="156"/>
+      <c r="D82" s="157"/>
+      <c r="E82" s="152"/>
+      <c r="F82" s="152"/>
+      <c r="G82" s="152"/>
+      <c r="H82" s="152"/>
+      <c r="I82" s="152"/>
+      <c r="J82" s="152"/>
+      <c r="K82" s="152"/>
+      <c r="L82" s="152"/>
+      <c r="M82" s="152"/>
+      <c r="N82" s="152"/>
+      <c r="O82" s="152"/>
+      <c r="P82" s="152"/>
+      <c r="Q82" s="152"/>
+      <c r="R82" s="152"/>
+      <c r="S82" s="152"/>
+      <c r="T82" s="163"/>
+      <c r="U82" s="164"/>
+      <c r="V82" s="164"/>
+      <c r="W82" s="164"/>
+      <c r="X82" s="164"/>
+      <c r="Y82" s="164"/>
+      <c r="Z82" s="164"/>
+      <c r="AA82" s="164"/>
+      <c r="AB82" s="164"/>
+      <c r="AC82" s="164"/>
+      <c r="AD82" s="164"/>
+      <c r="AE82" s="164"/>
+      <c r="AF82" s="164"/>
+      <c r="AG82" s="164"/>
+      <c r="AH82" s="164"/>
+      <c r="AI82" s="173"/>
+      <c r="AJ82" s="118"/>
       <c r="AK82" s="2"/>
     </row>
     <row r="83" ht="21" customHeight="1" spans="1:36">
       <c r="A83" s="12"/>
-      <c r="B83" s="161"/>
-      <c r="C83" s="162"/>
-      <c r="D83" s="163"/>
-      <c r="E83" s="164"/>
-      <c r="F83" s="162"/>
-      <c r="G83" s="162"/>
-      <c r="H83" s="162"/>
-      <c r="I83" s="162"/>
-      <c r="J83" s="162"/>
-      <c r="K83" s="162"/>
-      <c r="L83" s="162"/>
-      <c r="M83" s="162"/>
-      <c r="N83" s="162"/>
-      <c r="O83" s="162"/>
-      <c r="P83" s="162"/>
-      <c r="Q83" s="162"/>
-      <c r="R83" s="162"/>
-      <c r="S83" s="163"/>
+      <c r="B83" s="159"/>
+      <c r="C83" s="160"/>
+      <c r="D83" s="161"/>
+      <c r="E83" s="162"/>
+      <c r="F83" s="160"/>
+      <c r="G83" s="160"/>
+      <c r="H83" s="160"/>
+      <c r="I83" s="160"/>
+      <c r="J83" s="160"/>
+      <c r="K83" s="160"/>
+      <c r="L83" s="160"/>
+      <c r="M83" s="160"/>
+      <c r="N83" s="160"/>
+      <c r="O83" s="160"/>
+      <c r="P83" s="160"/>
+      <c r="Q83" s="160"/>
+      <c r="R83" s="160"/>
+      <c r="S83" s="161"/>
       <c r="T83" s="26"/>
-      <c r="U83" s="167"/>
-      <c r="V83" s="167"/>
-      <c r="W83" s="167"/>
-      <c r="X83" s="167"/>
-      <c r="Y83" s="167"/>
-      <c r="Z83" s="167"/>
-      <c r="AA83" s="167"/>
-      <c r="AB83" s="167"/>
-      <c r="AC83" s="167"/>
-      <c r="AD83" s="167"/>
-      <c r="AE83" s="167"/>
-      <c r="AF83" s="167"/>
-      <c r="AG83" s="167"/>
-      <c r="AH83" s="167"/>
-      <c r="AI83" s="176"/>
-      <c r="AJ83" s="177"/>
+      <c r="U83" s="165"/>
+      <c r="V83" s="165"/>
+      <c r="W83" s="165"/>
+      <c r="X83" s="165"/>
+      <c r="Y83" s="165"/>
+      <c r="Z83" s="165"/>
+      <c r="AA83" s="165"/>
+      <c r="AB83" s="165"/>
+      <c r="AC83" s="165"/>
+      <c r="AD83" s="165"/>
+      <c r="AE83" s="165"/>
+      <c r="AF83" s="165"/>
+      <c r="AG83" s="165"/>
+      <c r="AH83" s="165"/>
+      <c r="AI83" s="174"/>
+      <c r="AJ83" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="137">
